--- a/Deliverables/Engineering/Traceability/ENG-TRC-001_양방향 요구사항 추적 매트릭스.xlsx
+++ b/Deliverables/Engineering/Traceability/ENG-TRC-001_양방향 요구사항 추적 매트릭스.xlsx
@@ -211,7 +211,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="49">
+  <cellXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -307,6 +307,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0"/>
@@ -815,10 +821,14 @@
           <t>IT-0001~IT-0011, IT-0026~IT-0030, IT-0032~IT-0041, IT-0043 (ENG-SWE5-002, IF-0001/0002/0005/0006/0007 경로 — freshness 판정, 입력검증 거절, DEGRADED 전이, ASIL B 오류 주입 포함). 실행 결과: ENG-SWE5-003(Integration Results), 전량 Pass.</t>
         </is>
       </c>
-      <c r="H10" s="42" t="inlineStr"/>
-      <c r="I10" s="42" t="inlineStr">
-        <is>
-          <t>SWE.5까지 완료(2026-09-18) — IT-0001~IT-0043 43/43 Pass. 함수 커버리지 100%(31/31), 문/분기 커버리지 100%(coverage.py --branch, coverage_it.json). Call 커버리지 100%(아키텍처 호출관계 9/9: IF-0005~IF-0009는 coverage.py 줄 단위로 직접 실측, IF-0010~IF-0012는 coverage.py의 람다-튜플 표현식 줄 추적 한계로 인해 실물 계측(recordCalls)·오류주입 관측으로 보완 실측 — ENG-SWE5-001 7장/12장 참조). SWE.6은 이후 단계 대기.</t>
+      <c r="H10" s="49" t="inlineStr">
+        <is>
+          <t>ST-FUNC-0001~0008 (ENG-SWE6-001, SWR-013(a) 경계값분석 4건[199/200/201/300ms] + SWR-013(b) 동등분할/경계값분석 3건[누락/비수치/음수] + 오류추측 견고성 1건[ignition_on]). ST-FUNC-0009(제안)도 SWR-013(b) 분류를 공유(오류추측, 원문 비근거). 실행 결과: ENG-SWE6-002(Verification Results), 9/9 Pass(제안 케이스 포함).</t>
+        </is>
+      </c>
+      <c r="I10" s="49" t="inlineStr">
+        <is>
+          <t>SWE.6까지 완료(2026-09-18) — ST-FUNC-0001~0009 9/9 Pass(ENG-SWE6-002). SWR-013(a) 경계값(199/200/201/300ms) 전량 검증, SWR-013(b) 형식오류(누락/비수치)·범위오류(하한) 거절 검증. 적용 한계: source_timestamp_s 상한 range 판정식 미확정(요구사항 원문 미기재, 8장 가정 2)이라 상한 경계 시험 미실시 — 하한(0.0)만 검증. ignition_on 형식오류는 Phase1 CycleResult로 게이트(INPUT_INVALID) 효과가 직접 관측되지 않아(후보 명령 채널 부재) 비충돌만 확인 — 완전한 SWR-013(b) 게이트 검증은 candidateCommands 채널이 생기는 이후 Phase에서 보강 필요.</t>
         </is>
       </c>
     </row>
@@ -858,9 +868,14 @@
           <t>IT-0005~IT-0024, IT-0026~IT-0029, IT-0031~IT-0033, IT-0039~IT-0043 (ENG-SWE5-002, IF-0003/0004/0007/0008/0009/0010/0011 경로 — FAULT 판정/우선순위, 게이트 차단, fail-freeze, 경고 발행, ASIL B 오류 주입 포함). 실행 결과: ENG-SWE5-003, 전량 Pass.</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>SWE.5까지 완료(2026-09-18) — IT-0001~IT-0043 43/43 Pass. 함수 커버리지 100%(31/31), 문/분기 커버리지 100%(coverage.py --branch, coverage_it.json). Call 커버리지 100%(아키텍처 호출관계 9/9: IF-0005~IF-0009는 coverage.py 줄 단위로 직접 실측, IF-0010~IF-0012는 coverage.py의 람다-튜플 표현식 줄 추적 한계로 인해 실물 계측(recordCalls)·오류주입 관측으로 보완 실측 — ENG-SWE5-001 7장/12장 참조). SWE.6은 이후 단계 대기.</t>
+      <c r="H11" s="50" t="inlineStr">
+        <is>
+          <t>ST-FUNC-0010~0013 (ENG-SWE6-001, SWR-021(a) fail-freeze 2건[첫 주기+지속] + SWR-021(b) FAULT 전이·경고코드 2건[첫 전이+지속]). ST-FUNC-0009(제안)도 SWR-021(b) 관련 관측(sensor_fault 누락 시 FAULT)을 공유. 실행 결과: ENG-SWE6-002, 4/4 Pass(제안 케이스 별도 집계 ST-FUNC-0009 1건 포함 시 5/5).</t>
+        </is>
+      </c>
+      <c r="I11" s="50" t="inlineStr">
+        <is>
+          <t>SWE.6까지 완료(2026-09-18) — ST-FUNC-0009~0013 5/5 Pass(ENG-SWE6-002, ST-FUNC-0009는 SWR-013(b)/SWR-021(b) 제안 케이스로 두 행에 공유 표기). SWR-021(a) fail-freeze(첫 주기+지속) 검증, SWR-021(b) FAULT 전이+경고코드(첫 전이+지속) 검증. 적용 한계: 합격기준 비고의 "동일 주기 신규 명령 미반영" 시나리오는 Phase1에 후보 명령(candidateCommands) 채널 자체가 없어(항상 빈 리스트) 시험 대상에서 구조적으로 제외 — 이후 Phase에서 명령 채널이 추가되면 재검증 필요. DEGRADED/FAULT 상태 간 관계(복귀조건 등)는 요구사항 원문 미정(8장 가정 3)이라 시험 대상에서 제외.</t>
         </is>
       </c>
     </row>
@@ -891,7 +906,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1153,6 +1168,38 @@
         </is>
       </c>
       <c r="F13" t="inlineStr">
+        <is>
+          <t>미승인</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="50" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="B14" s="50" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="C14" s="50" t="inlineStr">
+        <is>
+          <t>sw-system-tester</t>
+        </is>
+      </c>
+      <c r="D14" s="50" t="inlineStr">
+        <is>
+          <t>Phase 1 시스템 테스트(SWE.6) — ENG-SWE6-001/002 작성, SWE.6/Coverage 열 갱신 (SWR-013/SWR-021 대상, ST-FUNC-0001~0013 13/13 Pass). SWR-013/SWR-021 두 요구사항의 추적 사슬이 SWE.6까지 완성됨.</t>
+        </is>
+      </c>
+      <c r="E14" s="50" t="inlineStr">
+        <is>
+          <t>초안(검토 미실시)</t>
+        </is>
+      </c>
+      <c r="F14" s="50" t="inlineStr">
         <is>
           <t>미승인</t>
         </is>

--- a/Deliverables/Engineering/Traceability/ENG-TRC-001_양방향 요구사항 추적 매트릭스.xlsx
+++ b/Deliverables/Engineering/Traceability/ENG-TRC-001_양방향 요구사항 추적 매트릭스.xlsx
@@ -211,7 +211,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -312,6 +312,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -616,7 +619,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I11"/>
+  <dimension ref="A1:I18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -701,7 +704,7 @@
       </c>
       <c r="F4" s="9" t="inlineStr">
         <is>
-          <t>v0.1 (Draft) — Phase 1 최초 작성</t>
+          <t>v0.2 (Draft) — Phase 2(안전 긴급 대응) 갱신, Phase 1 내용 유지</t>
         </is>
       </c>
       <c r="G4" s="9" t="str"/>
@@ -876,6 +879,195 @@
       <c r="I11" s="50" t="inlineStr">
         <is>
           <t>SWE.6까지 완료(2026-09-18) — ST-FUNC-0009~0013 5/5 Pass(ENG-SWE6-002, ST-FUNC-0009는 SWR-013(b)/SWR-021(b) 제안 케이스로 두 행에 공유 표기). SWR-021(a) fail-freeze(첫 주기+지속) 검증, SWR-021(b) FAULT 전이+경고코드(첫 전이+지속) 검증. 적용 한계: 합격기준 비고의 "동일 주기 신규 명령 미반영" 시나리오는 Phase1에 후보 명령(candidateCommands) 채널 자체가 없어(항상 빈 리스트) 시험 대상에서 구조적으로 제외 — 이후 Phase에서 명령 채널이 추가되면 재검증 필요. DEGRADED/FAULT 상태 간 관계(복귀조건 등)는 요구사항 원문 미정(8장 가정 3)이라 시험 대상에서 제외.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="34" customHeight="1">
+      <c r="A12" s="51" t="inlineStr">
+        <is>
+          <t>OEM-SR-001</t>
+        </is>
+      </c>
+      <c r="B12" s="51" t="inlineStr">
+        <is>
+          <t>SWR-007</t>
+        </is>
+      </c>
+      <c r="C12" s="51" t="inlineStr">
+        <is>
+          <t>ARC-0001, ARC-0004, ARC-0005, ARC-0009, ARC-0010 (IF-0005, IF-0008, IF-0009, IF-0013, IF-0016)</t>
+        </is>
+      </c>
+      <c r="D12" s="51" t="n"/>
+      <c r="E12" s="51" t="n"/>
+      <c r="F12" s="51" t="n"/>
+      <c r="G12" s="51" t="n"/>
+      <c r="H12" s="51" t="n"/>
+      <c r="I12" s="51" t="inlineStr">
+        <is>
+          <t>SWE.2(아키텍처 설계)까지 완료(2026-09-19) — Detailed Design/Code/SWE.4/SWE.5/SWE.6는 아직 해당 단계 아님(Phase 2 SWE.3 이후 게이트에서 채움). SWR-007(crash_status CONFIRMED 300ms 이내 최우선 긴급해제)의 우선순위 관계(3장)는 정량적 Command Arbiter 규칙이 SWE.2에서 확정되기 전까지 질적 서술만 존재.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="34" customHeight="1">
+      <c r="A13" s="51" t="inlineStr">
+        <is>
+          <t>OEM-SR-001</t>
+        </is>
+      </c>
+      <c r="B13" s="51" t="inlineStr">
+        <is>
+          <t>SWR-008</t>
+        </is>
+      </c>
+      <c r="C13" s="51" t="inlineStr">
+        <is>
+          <t>ARC-0010 (IF-0016)</t>
+        </is>
+      </c>
+      <c r="D13" s="51" t="n"/>
+      <c r="E13" s="51" t="n"/>
+      <c r="F13" s="51" t="n"/>
+      <c r="G13" s="51" t="n"/>
+      <c r="H13" s="51" t="n"/>
+      <c r="I13" s="51" t="inlineStr">
+        <is>
+          <t>SWE.2(아키텍처 설계)까지 완료(2026-09-19) — Detailed Design/Code/SWE.4/SWE.5/SWE.6는 아직 해당 단계 아님(Phase 2 SWE.3 이후 게이트에서 채움). SWR-008(crash_status PENDING 중 긴급해제 미개시)은 OEM-SR-001 원문에 직접 기술되지 않은 추론 요구사항(8장 가정 6) — OEM-A 확인 필요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="34" customHeight="1">
+      <c r="A14" s="51" t="inlineStr">
+        <is>
+          <t>OEM-SR-002</t>
+        </is>
+      </c>
+      <c r="B14" s="51" t="inlineStr">
+        <is>
+          <t>SWR-005</t>
+        </is>
+      </c>
+      <c r="C14" s="51" t="inlineStr">
+        <is>
+          <t>ARC-0001, ARC-0005, ARC-0009, ARC-0011 (IF-0005, IF-0008, IF-0014, IF-0017)</t>
+        </is>
+      </c>
+      <c r="D14" s="51" t="n"/>
+      <c r="E14" s="51" t="n"/>
+      <c r="F14" s="51" t="n"/>
+      <c r="G14" s="51" t="n"/>
+      <c r="H14" s="51" t="n"/>
+      <c r="I14" s="51" t="inlineStr">
+        <is>
+          <t>SWE.2(아키텍처 설계)까지 완료(2026-09-19) — Detailed Design/Code/SWE.4/SWE.5/SWE.6는 아직 해당 단계 아님(Phase 2 SWE.3 이후 게이트에서 채움). SWR-005(접근위험 도어 LOCK 및 해제요청 억제).</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="34" customHeight="1">
+      <c r="A15" s="51" t="inlineStr">
+        <is>
+          <t>OEM-SR-002</t>
+        </is>
+      </c>
+      <c r="B15" s="51" t="inlineStr">
+        <is>
+          <t>SWR-006</t>
+        </is>
+      </c>
+      <c r="C15" s="51" t="inlineStr">
+        <is>
+          <t>ARC-0005, ARC-0009, ARC-0011, ARC-0012 (IF-0008, IF-0017, IF-0018)</t>
+        </is>
+      </c>
+      <c r="D15" s="51" t="n"/>
+      <c r="E15" s="51" t="n"/>
+      <c r="F15" s="51" t="n"/>
+      <c r="G15" s="51" t="n"/>
+      <c r="H15" s="51" t="n"/>
+      <c r="I15" s="51" t="inlineStr">
+        <is>
+          <t>SWE.2(아키텍처 설계)까지 완료(2026-09-19) — Detailed Design/Code/SWE.4/SWE.5/SWE.6는 아직 해당 단계 아님(Phase 2 SWE.3 이후 게이트에서 채움). SWR-006(10초 이내 재입력 override)은 OEM-SR-002(ASIL B)와 OEM-FR-003(QM) 두 상위 출처를 가지는 혼합 분류 요구사항(8장 가정 8) — 바로 아래 OEM-FR-003 행과 SWR-006을 공유함.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="34" customHeight="1">
+      <c r="A16" s="51" t="inlineStr">
+        <is>
+          <t>OEM-FR-003</t>
+        </is>
+      </c>
+      <c r="B16" s="51" t="inlineStr">
+        <is>
+          <t>SWR-006</t>
+        </is>
+      </c>
+      <c r="C16" s="51" t="inlineStr">
+        <is>
+          <t>ARC-0005, ARC-0009, ARC-0011, ARC-0012 (IF-0008, IF-0017, IF-0018)</t>
+        </is>
+      </c>
+      <c r="D16" s="51" t="n"/>
+      <c r="E16" s="51" t="n"/>
+      <c r="F16" s="51" t="n"/>
+      <c r="G16" s="51" t="n"/>
+      <c r="H16" s="51" t="n"/>
+      <c r="I16" s="51" t="inlineStr">
+        <is>
+          <t>SWE.2(아키텍처 설계)까지 완료(2026-09-19) — Detailed Design/Code/SWE.4/SWE.5/SWE.6는 아직 해당 단계 아님(Phase 2 SWE.3 이후 게이트에서 채움). 위 OEM-SR-002 행과 SWR-006을 공유(혼합 상위출처, 8장 가정 8). override 발생 시 실제 출력 RELEASE 전환 여부는 원문 미기재로 확인 필요(8장 가정 7).</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="34" customHeight="1">
+      <c r="A17" s="51" t="inlineStr">
+        <is>
+          <t>OEM-SR-002</t>
+        </is>
+      </c>
+      <c r="B17" s="51" t="inlineStr">
+        <is>
+          <t>SWR-009</t>
+        </is>
+      </c>
+      <c r="C17" s="51" t="inlineStr">
+        <is>
+          <t>ARC-0011 (IF-0017)</t>
+        </is>
+      </c>
+      <c r="D17" s="51" t="n"/>
+      <c r="E17" s="51" t="n"/>
+      <c r="F17" s="51" t="n"/>
+      <c r="G17" s="51" t="n"/>
+      <c r="H17" s="51" t="n"/>
+      <c r="I17" s="51" t="inlineStr">
+        <is>
+          <t>SWE.2(아키텍처 설계)까지 완료(2026-09-19) — Detailed Design/Code/SWE.4/SWE.5/SWE.6는 아직 해당 단계 아님(Phase 2 SWE.3 이후 게이트에서 채움). SWR-009(좌우 접근위험 독립 처리).</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="34" customHeight="1">
+      <c r="A18" s="51" t="inlineStr">
+        <is>
+          <t>OEM-FR-005</t>
+        </is>
+      </c>
+      <c r="B18" s="51" t="inlineStr">
+        <is>
+          <t>SWR-017</t>
+        </is>
+      </c>
+      <c r="C18" s="51" t="inlineStr">
+        <is>
+          <t>ARC-0001, ARC-0005, ARC-0009, ARC-0013 (IF-0005, IF-0008, IF-0015, IF-0019)</t>
+        </is>
+      </c>
+      <c r="D18" s="51" t="n"/>
+      <c r="E18" s="51" t="n"/>
+      <c r="F18" s="51" t="n"/>
+      <c r="G18" s="51" t="n"/>
+      <c r="H18" s="51" t="n"/>
+      <c r="I18" s="51" t="inlineStr">
+        <is>
+          <t>SWE.2(아키텍처 설계)까지 완료(2026-09-19) — Detailed Design/Code/SWE.4/SWE.5/SWE.6는 아직 해당 단계 아님(Phase 2 SWE.3 이후 게이트에서 채움). SWR-017(화재/과온/성인탑승 확인 시 강제해제). 이유코드 카탈로그 미확정(8장 가정 12).</t>
         </is>
       </c>
     </row>
@@ -906,7 +1098,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1202,6 +1394,70 @@
       <c r="F14" s="50" t="inlineStr">
         <is>
           <t>미승인</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>0.6</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>requirements-analyst</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Phase 2 갱신 — OEM-SR-001(→SWR-007/008), OEM-SR-002(→SWR-005/006/009), OEM-FR-003(→SWR-006, OEM-SR-002와 공유), OEM-FR-005(→SWR-017)의 Upper Req/SW Req 행 7건 추가 (ENG-SWE1-001 Phase 2 갱신과 함께).</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>초안(검토 미실시)</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>미승인</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>0.7</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>orchestrator (session)</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>아키텍처 서브에이전트가 중단된 지점(Architecture 열 미기재)을 ENG-SWE2-001 12/14장 매핑 그대로 완성</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>초안(검토 미실시)</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>확인 필요(미지정)</t>
         </is>
       </c>
     </row>

--- a/Deliverables/Engineering/Traceability/ENG-TRC-001_양방향 요구사항 추적 매트릭스.xlsx
+++ b/Deliverables/Engineering/Traceability/ENG-TRC-001_양방향 요구사항 추적 매트릭스.xlsx
@@ -811,12 +811,12 @@
       </c>
       <c r="E10" s="42" t="inlineStr">
         <is>
-          <t>IU-0001: src/ngv/adapters/input_validation_adapter.py::InputValidationAdapter (validateTimestampField/validateBooleanField/applySensorFaultFailSafe/normalizeCycle/handleCycle); IU-0002: src/ngv/core/freshness_monitor.py::FreshnessMonitor(evaluate/reset); IU-0003: src/ngv/core/state_manager.py::StateManager(evaluate/reset); IU-0009: src/ngv/app/safety_kernel_orchestrator.py::SafetyKernelOrchestrator(evaluateCycle/reset)</t>
+          <t>IU-0001: src/ngv/adapters/input_validation_adapter.py::InputValidationAdapter (validateTimestampField/validateBooleanField/applySensorFaultFailSafe/normalizeCycle/handleCycle); IU-0002: src/ngv/core/freshness_monitor.py::FreshnessMonitor(evaluate/reset); IU-0003: src/ngv/core/state_manager.py::StateManager(evaluate/reset); IU-0009: src/ngv/app/safety_kernel_orchestrator.py::SafetyKernelOrchestrator(evaluateCycle/reset)  [Phase2 갱신 각주(2026-09-19)] IU-0001.normalizeCycle()은 9필드로 확장되었으나 SWR-013(a)/(b) 판정 로직 자체는 변경 없음(Phase2 6필드는 별도 하류 IU-0010~0013이 소비). IU-0009.evaluateCycle()은 IU-0010~0013 호출과 candidateCommands 조립 단계가 추가되었으나 freshness/state 판정 순서와 SWR-013 관련 동작은 동일하게 유지됨. 회귀 확인: tests/test_input_validation_adapter.py::TestNormalizeCycle(신규 2건 포함 총 9건), tests/test_safety_kernel_orchestrator.py 전량 Pass(품질 게이트 통과, 행 12~18 Coverage 참조).</t>
         </is>
       </c>
       <c r="F10" s="42" t="inlineStr">
         <is>
-          <t>tests/test_input_validation_adapter.py; tests/test_freshness_monitor.py; tests/test_state_manager.py; tests/test_safety_kernel_orchestrator.py (unittest, 42 테스트, 전량 Positive+Negative — test-annotation.md 형식 준수)</t>
+          <t>tests/test_input_validation_adapter.py; tests/test_freshness_monitor.py; tests/test_state_manager.py; tests/test_safety_kernel_orchestrator.py (unittest, 42 테스트, 전량 Positive+Negative — test-annotation.md 형식 준수) tests/test_input_validation_adapter.py; tests/test_safety_kernel_orchestrator.py(Phase2 갱신 후 회귀 없음, 2026-09-19 재확인)</t>
         </is>
       </c>
       <c r="G10" s="42" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>IU-0003: src/ngv/core/state_manager.py::StateManager(evaluate/reset); IU-0004: src/ngv/core/output_hold_actuator.py::OutputHoldActuator(confirm/reset/getLastConfirmedOutput); IU-0005: src/ngv/core/command_arbiter.py::CommandArbiter(arbitrate) [최소구현: 게이트만, Phase1]; IU-0007: src/ngv/adapters/notification_adapter.py::NotificationAdapter(publishWarning) [최소구현: 패스스루]; IU-0009: src/ngv/app/safety_kernel_orchestrator.py::SafetyKernelOrchestrator(evaluateCycle/reset)</t>
+          <t>IU-0003: src/ngv/core/state_manager.py::StateManager(evaluate/reset); IU-0004: src/ngv/core/output_hold_actuator.py::OutputHoldActuator(confirm/reset/getLastConfirmedOutput); IU-0005: src/ngv/core/command_arbiter.py::CommandArbiter(arbitrate) [최소구현: 게이트만, Phase1]; IU-0007: src/ngv/adapters/notification_adapter.py::NotificationAdapter(publishWarning) [최소구현: 패스스루]; IU-0009: src/ngv/app/safety_kernel_orchestrator.py::SafetyKernelOrchestrator(evaluateCycle/reset)  [Phase2 갱신 각주(2026-09-19)] IU-0005.arbitrate()는 5.2절에 따라 "candidateCommands 비어있지 않으면 NotImplementedError" 계약을 완전히 폐기하고 문(door)별 최소-priority 후보 선택 알고리즘(selectForDoor(), 동일 priority 충돌 시 ValueError)으로 대체됨 — 하위호환 아님. SWR-021(a)/(b) 게이트(FAULT/inputInvalid 최우선) 자체는 변경 없이 유지. 기존 tests/test_command_arbiter.py의 NotImplementedError 검증 테스트는 새 계약을 검증하도록 전면 재작성됨(10건, TDD Red-Green 확인). IU-0007(패스스루)은 Phase2 이유코드 미발행으로 변경 없음.</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>tests/test_state_manager.py; tests/test_output_hold_actuator.py; tests/test_command_arbiter.py; tests/test_notification_adapter.py; tests/test_safety_kernel_orchestrator.py (unittest, IU-0005/0007은 Phase1 최소계약 범위만 검증)</t>
+          <t>tests/test_state_manager.py; tests/test_output_hold_actuator.py; tests/test_command_arbiter.py; tests/test_notification_adapter.py; tests/test_safety_kernel_orchestrator.py (unittest, IU-0005/0007은 Phase1 최소계약 범위만 검증) tests/test_command_arbiter.py(전면 재작성, 10건); tests/test_safety_kernel_orchestrator.py(Phase2 갱신 후 회귀 없음)</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -898,14 +898,34 @@
           <t>ARC-0001, ARC-0004, ARC-0005, ARC-0009, ARC-0010 (IF-0005, IF-0008, IF-0009, IF-0013, IF-0016)</t>
         </is>
       </c>
-      <c r="D12" s="51" t="n"/>
-      <c r="E12" s="51" t="n"/>
-      <c r="F12" s="51" t="n"/>
-      <c r="G12" s="51" t="n"/>
-      <c r="H12" s="51" t="n"/>
-      <c r="I12" s="51" t="inlineStr">
-        <is>
-          <t>SWE.2(아키텍처 설계)까지 완료(2026-09-19) — Detailed Design/Code/SWE.4/SWE.5/SWE.6는 아직 해당 단계 아님(Phase 2 SWE.3 이후 게이트에서 채움). SWR-007(crash_status CONFIRMED 300ms 이내 최우선 긴급해제)의 우선순위 관계(3장)는 정량적 Command Arbiter 규칙이 SWE.2에서 확정되기 전까지 질적 서술만 존재.</t>
+      <c r="D12" s="51" t="inlineStr">
+        <is>
+          <t>IU-0001, IU-0004, IU-0005, IU-0009, IU-0010(신규)</t>
+        </is>
+      </c>
+      <c r="E12" s="51" t="inlineStr">
+        <is>
+          <t>IU-0010: src/ngv/core/crash_monitor.py::CrashMonitor(evaluate); IU-0001: src/ngv/adapters/input_validation_adapter.py::InputValidationAdapter(validateCrashStatusField[신규]/normalizeCycle[갱신, 9필드]); IU-0005: src/ngv/core/command_arbiter.py::CommandArbiter(arbitrate/selectForDoor)[갱신, 계약 대체]; IU-0004: src/ngv/core/output_hold_actuator.py::OutputHoldActuator(confirm)[변경 없음]; IU-0009: src/ngv/app/safety_kernel_orchestrator.py::SafetyKernelOrchestrator(evaluateCycle/evaluatePhase2Candidates/assembleCandidateCommands)[갱신]</t>
+        </is>
+      </c>
+      <c r="F12" s="51" t="inlineStr">
+        <is>
+          <t>tests/test_crash_monitor.py(5, CONFIRMED→RELEASE 후보/priority=1 포함); tests/test_input_validation_adapter.py::TestValidateCrashStatusField(5); tests/test_command_arbiter.py(10, 전면 재작성 — 5.2절 계약 대체 반영); tests/test_safety_kernel_orchestrator.py::TestSafetyKernelOrchestratorPhase2Wiring::testCrashConfirmedProducesReleaseOnBothDoors(종단 검증, 300ms 예산 여유분석은 6.1b절 근거로 별도 타이밍 시험 불필요)</t>
+        </is>
+      </c>
+      <c r="G12" s="51" t="inlineStr">
+        <is>
+          <t>IT-0044, IT-0046~IT-0048(IF-0016 판정), IT-0069, IT-0073, IT-0082, IT-0086~0089, IT-0092(우선순위 중재·게이트·전체 체인), IT-0075~0078, IT-0093(IF-0013 입력검증) (ENG-SWE5-002). 실행 결과: ENG-SWE5-003, 전량 Pass.</t>
+        </is>
+      </c>
+      <c r="H12" s="49" t="inlineStr">
+        <is>
+          <t>ST-FUNC-0018~0020 (ENG-SWE6-001, SWR-007(a) 경계값분석 1건[300ms 예산, 평가주기 간격 스트레스] + 결정표기반 시험 1건[crash vs 접근위험 우선순위] + 상태전이 테스트 1건[RELEASE 지속]). 실행 결과: ENG-SWE6-002(Verification Results), 3/3 Pass.</t>
+        </is>
+      </c>
+      <c r="I12" s="49" t="inlineStr">
+        <is>
+          <t>SWE.6까지 완료(2026-09-19, sw-system-tester) — ST-FUNC-0018~0020 3/3 Pass(ENG-SWE6-002). SWR-007(a) 300ms 예산(즉시 반영, crash_monitor에 elapsed-time 게이트 없음 확인) 및 최우선 순위(crash&gt;접근위험) 검증, SWR-007(b) RELEASE 지속(경쟁 조건 등장 후에도 유지) 검증. 적용 한계: 복수 조건 동시발생의 전수 조합은 아님(3장 우선순위 관계로 도출 가능한 대표 시나리오만 검증). 요구사항 커버리지: SWR-007 SWE.6까지 완료.</t>
         </is>
       </c>
     </row>
@@ -925,14 +945,34 @@
           <t>ARC-0010 (IF-0016)</t>
         </is>
       </c>
-      <c r="D13" s="51" t="n"/>
-      <c r="E13" s="51" t="n"/>
-      <c r="F13" s="51" t="n"/>
-      <c r="G13" s="51" t="n"/>
-      <c r="H13" s="51" t="n"/>
-      <c r="I13" s="51" t="inlineStr">
-        <is>
-          <t>SWE.2(아키텍처 설계)까지 완료(2026-09-19) — Detailed Design/Code/SWE.4/SWE.5/SWE.6는 아직 해당 단계 아님(Phase 2 SWE.3 이후 게이트에서 채움). SWR-008(crash_status PENDING 중 긴급해제 미개시)은 OEM-SR-001 원문에 직접 기술되지 않은 추론 요구사항(8장 가정 6) — OEM-A 확인 필요.</t>
+      <c r="D13" s="51" t="inlineStr">
+        <is>
+          <t>IU-0010(신규)</t>
+        </is>
+      </c>
+      <c r="E13" s="51" t="inlineStr">
+        <is>
+          <t>IU-0010: src/ngv/core/crash_monitor.py::CrashMonitor(evaluate)</t>
+        </is>
+      </c>
+      <c r="F13" s="51" t="inlineStr">
+        <is>
+          <t>tests/test_crash_monitor.py::TestCrashMonitorEvaluate::testPendingStatusAppliesHoldWithoutReleaseCandidate(PENDING→releaseCandidate=None/pendingHoldApplied=True)</t>
+        </is>
+      </c>
+      <c r="G13" s="51" t="inlineStr">
+        <is>
+          <t>IT-0045(PENDING 보류 판정, ENG-SWE5-002). 실행 결과: ENG-SWE5-003, Pass.</t>
+        </is>
+      </c>
+      <c r="H13" s="49" t="inlineStr">
+        <is>
+          <t>ST-FUNC-0021~0022 (ENG-SWE6-001, SWR-008 동등분할 1건[PENDING 클래스] + 요구사항 기반 시험 1건[SWR-008/SWR-017 상호작용]). 실행 결과: ENG-SWE6-002, 2/2 Pass.</t>
+        </is>
+      </c>
+      <c r="I13" s="49" t="inlineStr">
+        <is>
+          <t>SWE.6까지 완료(2026-09-19, sw-system-tester) — ST-FUNC-0021~0022 2/2 Pass(ENG-SWE6-002). PENDING이 긴급해제를 조기 개시하지 않고 다른 SWR(SWR-017)의 독립 로직도 차단하지 않음을 확인. 적용 한계: 본 요구사항 자체가 OEM 원문 비명시 추론 요구사항(ENG-SWE1-001 8장 가정 6, OEM-A 확인 필요) — 시스템 시험도 이 추론을 그대로 전제로 함. 요구사항 커버리지: SWR-008 SWE.6까지 완료.</t>
         </is>
       </c>
     </row>
@@ -952,14 +992,34 @@
           <t>ARC-0001, ARC-0005, ARC-0009, ARC-0011 (IF-0005, IF-0008, IF-0014, IF-0017)</t>
         </is>
       </c>
-      <c r="D14" s="51" t="n"/>
-      <c r="E14" s="51" t="n"/>
-      <c r="F14" s="51" t="n"/>
-      <c r="G14" s="51" t="n"/>
-      <c r="H14" s="51" t="n"/>
-      <c r="I14" s="51" t="inlineStr">
-        <is>
-          <t>SWE.2(아키텍처 설계)까지 완료(2026-09-19) — Detailed Design/Code/SWE.4/SWE.5/SWE.6는 아직 해당 단계 아님(Phase 2 SWE.3 이후 게이트에서 채움). SWR-005(접근위험 도어 LOCK 및 해제요청 억제).</t>
+      <c r="D14" s="51" t="inlineStr">
+        <is>
+          <t>IU-0001, IU-0005, IU-0009, IU-0011(신규)</t>
+        </is>
+      </c>
+      <c r="E14" s="51" t="inlineStr">
+        <is>
+          <t>IU-0011: src/ngv/core/approach_risk_evaluator.py::ApproachRiskEvaluator(evaluate/evaluateSide); IU-0001/IU-0005/IU-0009: 상동(행 12와 동일 갱신분 공유)</t>
+        </is>
+      </c>
+      <c r="F14" s="51" t="inlineStr">
+        <is>
+          <t>tests/test_approach_risk_evaluator.py(6, SWR-009 4조합 FF/FT/TF/TT 전수 포함); tests/test_safety_kernel_orchestrator.py::TestSafetyKernelOrchestratorPhase2Wiring::testLeftApproachRiskLocksOnlyLeftDoor(종단 검증)</t>
+        </is>
+      </c>
+      <c r="G14" s="51" t="inlineStr">
+        <is>
+          <t>IT-0049~0054(IF-0017 억제 판정), IT-0070~0071(우선순위·문별 독립성), IT-0079(IF-0014 입력검증), IT-0083(전체 체인) (ENG-SWE5-002). 실행 결과: ENG-SWE5-003, 전량 Pass.</t>
+        </is>
+      </c>
+      <c r="H14" s="49" t="inlineStr">
+        <is>
+          <t>ST-FUNC-0014~0015 (ENG-SWE6-001, SWR-005(a) 요구사항 기반 시험 1건[단일 도어 LOCK] + SWR-005(b) 결정표기반/오류추측 1건[경쟁 RELEASE 후보 억제]). SWR-009 4조합(ST-FUNC-0023~0026)의 TF/FT 케이스도 SWR-005(a) 관측을 겸함. 실행 결과: ENG-SWE6-002, 2/2 Pass(겸용 케이스 포함 시 4/4).</t>
+        </is>
+      </c>
+      <c r="I14" s="49" t="inlineStr">
+        <is>
+          <t>SWE.6까지 완료(2026-09-19, sw-system-tester) — ST-FUNC-0014~0015 2/2 Pass(ENG-SWE6-002). 접근위험 TRUE 시 LOCK 전환(a) 및 경쟁 RELEASE 후보 대비 억제 유지(b, 우선순위 기반 간접 검증) 확인. 적용 한계: 원문의 "해제 요청"은 통상 운전자 수동명령(OEM-FR-001)을 뜻하나 이 채널은 Phase2 범위 밖(1.3절)이라 직접 재현 불가 — 경쟁 RELEASE 후보(SWR-017)로 대체 검증. 이유코드(억제 사유) 기록은 CycleResult 미노출(ledger 갭 10)로 시스템 경계에서 직접 관측 불가(하위 IT-0049~0054/0079/0083에서 이미 검증됨). 요구사항 커버리지: SWR-005 SWE.6까지 완료.</t>
         </is>
       </c>
     </row>
@@ -979,14 +1039,34 @@
           <t>ARC-0005, ARC-0009, ARC-0011, ARC-0012 (IF-0008, IF-0017, IF-0018)</t>
         </is>
       </c>
-      <c r="D15" s="51" t="n"/>
-      <c r="E15" s="51" t="n"/>
-      <c r="F15" s="51" t="n"/>
-      <c r="G15" s="51" t="n"/>
-      <c r="H15" s="51" t="n"/>
-      <c r="I15" s="51" t="inlineStr">
-        <is>
-          <t>SWE.2(아키텍처 설계)까지 완료(2026-09-19) — Detailed Design/Code/SWE.4/SWE.5/SWE.6는 아직 해당 단계 아님(Phase 2 SWE.3 이후 게이트에서 채움). SWR-006(10초 이내 재입력 override)은 OEM-SR-002(ASIL B)와 OEM-FR-003(QM) 두 상위 출처를 가지는 혼합 분류 요구사항(8장 가정 8) — 바로 아래 OEM-FR-003 행과 SWR-006을 공유함.</t>
+      <c r="D15" s="51" t="inlineStr">
+        <is>
+          <t>IU-0005, IU-0009, IU-0011, IU-0012(신규)</t>
+        </is>
+      </c>
+      <c r="E15" s="51" t="inlineStr">
+        <is>
+          <t>IU-0011: src/ngv/core/approach_risk_evaluator.py::ApproachRiskEvaluator(evaluate); IU-0012: src/ngv/core/approach_risk_override_manager.py::ApproachRiskOverrideManager(decide/decideSide/reset)[유일한 상태 보유]; IU-0009: src/ngv/app/safety_kernel_orchestrator.py::SafetyKernelOrchestrator(evaluatePhase2Candidates/assembleCandidateCommands/reset)</t>
+        </is>
+      </c>
+      <c r="F15" s="51" t="inlineStr">
+        <is>
+          <t>tests/test_approach_risk_override_manager.py(8, 10.0s/10.1s 경계값분석 포함 — SWR-006(a)/(b) 문언 경계, 리셋 규칙 testResetClearsSuppressionTimerEvenWhileRiskStaysActive 포함); tests/test_safety_kernel_orchestrator.py::TestSafetyKernelOrchestratorReset::testResetClearsOverrideManagerSuppressionTimer; tests/test_safety_kernel_orchestrator.py::TestSafetyKernelOrchestratorAssembleCandidateCommands::testExcludesLeftSuppressCandidateWhenLeftOverrideActive(override의 LOCK 후보 철회, 비강제 확인)</t>
+        </is>
+      </c>
+      <c r="G15" s="51" t="inlineStr">
+        <is>
+          <t>IT-0055~0061(IF-0018 override 판정, 10s 경계값·타이머 리셋·좌우 독립), IT-0084(전체 체인 placeholder 한계 실증) (ENG-SWE5-002). 실행 결과: ENG-SWE5-003, 전량 Pass.</t>
+        </is>
+      </c>
+      <c r="H15" s="49" t="inlineStr">
+        <is>
+          <t>ST-FUNC-0016~0017 (ENG-SWE6-001, SWR-006(a) 경계값분석 1건[10초 이내 경계, elapsed=10.000s] + SWR-006(b) 경계값분석 1건[10초 초과 경계, elapsed=10.100s]). 실행 결과: ENG-SWE6-002, 1/2 Pass(ST-FUNC-0016 Fail).</t>
+        </is>
+      </c>
+      <c r="I15" s="49" t="inlineStr">
+        <is>
+          <t>SWE.6까지 완료(2026-09-19, sw-system-tester) — ST-FUNC-0016~0017 1/2 Pass(ENG-SWE6-002). ST-FUNC-0016(10초 이내 override 생성, SWR-006a)은 Fail — releaseReRequested 채널이 원시 입력에 없고(OEM-FR-001 미분석, ledger 갭 7) CycleResult가 override 상태/이유코드를 노출하지 않아(ledger 갭 10) 시스템 경계에서 SWR-006(a) 성립을 확인할 수 없음(근본원인은 기지 구조적 갭이며, IT-0084가 통합 수준에서 이미 이 한계를 문서화). ST-FUNC-0017(10초 초과, 억제 유지, SWR-006b)은 Pass. [갭] SWR-006(a)는 SWE.6 단계에서 시스템 경계 기준으로는 합격 판정에 도달하지 못했다(Fail) — OEM-FR-001 분석(Phase4 예정) 및 CycleResult의 override 상태 노출 확장 후 재검증 필요. 요구사항 커버리지: SWR-006 SWE.6까지 완료(단, (a) Fail).</t>
         </is>
       </c>
     </row>
@@ -1006,14 +1086,34 @@
           <t>ARC-0005, ARC-0009, ARC-0011, ARC-0012 (IF-0008, IF-0017, IF-0018)</t>
         </is>
       </c>
-      <c r="D16" s="51" t="n"/>
-      <c r="E16" s="51" t="n"/>
-      <c r="F16" s="51" t="n"/>
-      <c r="G16" s="51" t="n"/>
-      <c r="H16" s="51" t="n"/>
-      <c r="I16" s="51" t="inlineStr">
-        <is>
-          <t>SWE.2(아키텍처 설계)까지 완료(2026-09-19) — Detailed Design/Code/SWE.4/SWE.5/SWE.6는 아직 해당 단계 아님(Phase 2 SWE.3 이후 게이트에서 채움). 위 OEM-SR-002 행과 SWR-006을 공유(혼합 상위출처, 8장 가정 8). override 발생 시 실제 출력 RELEASE 전환 여부는 원문 미기재로 확인 필요(8장 가정 7).</t>
+      <c r="D16" s="51" t="inlineStr">
+        <is>
+          <t>IU-0005, IU-0009, IU-0011, IU-0012(신규)</t>
+        </is>
+      </c>
+      <c r="E16" s="51" t="inlineStr">
+        <is>
+          <t>IU-0011: src/ngv/core/approach_risk_evaluator.py::ApproachRiskEvaluator(evaluate); IU-0012: src/ngv/core/approach_risk_override_manager.py::ApproachRiskOverrideManager(decide/decideSide/reset)[유일한 상태 보유]; IU-0009: src/ngv/app/safety_kernel_orchestrator.py::SafetyKernelOrchestrator(evaluatePhase2Candidates/assembleCandidateCommands/reset)</t>
+        </is>
+      </c>
+      <c r="F16" s="51" t="inlineStr">
+        <is>
+          <t>tests/test_approach_risk_override_manager.py(8, 10.0s/10.1s 경계값분석 포함 — SWR-006(a)/(b) 문언 경계, 리셋 규칙 testResetClearsSuppressionTimerEvenWhileRiskStaysActive 포함); tests/test_safety_kernel_orchestrator.py::TestSafetyKernelOrchestratorReset::testResetClearsOverrideManagerSuppressionTimer; tests/test_safety_kernel_orchestrator.py::TestSafetyKernelOrchestratorAssembleCandidateCommands::testExcludesLeftSuppressCandidateWhenLeftOverrideActive(override의 LOCK 후보 철회, 비강제 확인)</t>
+        </is>
+      </c>
+      <c r="G16" s="51" t="inlineStr">
+        <is>
+          <t>IT-0055~0061, IT-0084 (행 15와 동일 공유, ENG-SWE5-002). 실행 결과: ENG-SWE5-003, 전량 Pass.</t>
+        </is>
+      </c>
+      <c r="H16" s="49" t="inlineStr">
+        <is>
+          <t>ST-FUNC-0016~0017 (ENG-SWE6-001, SWR-006(a) 경계값분석 1건[10초 이내 경계, elapsed=10.000s] + SWR-006(b) 경계값분석 1건[10초 초과 경계, elapsed=10.100s]). 실행 결과: ENG-SWE6-002, 1/2 Pass(ST-FUNC-0016 Fail).</t>
+        </is>
+      </c>
+      <c r="I16" s="49" t="inlineStr">
+        <is>
+          <t>SWE.6까지 완료(2026-09-19, sw-system-tester) — ST-FUNC-0016~0017 1/2 Pass(ENG-SWE6-002). ST-FUNC-0016(10초 이내 override 생성, SWR-006a)은 Fail — releaseReRequested 채널이 원시 입력에 없고(OEM-FR-001 미분석, ledger 갭 7) CycleResult가 override 상태/이유코드를 노출하지 않아(ledger 갭 10) 시스템 경계에서 SWR-006(a) 성립을 확인할 수 없음(근본원인은 기지 구조적 갭이며, IT-0084가 통합 수준에서 이미 이 한계를 문서화). ST-FUNC-0017(10초 초과, 억제 유지, SWR-006b)은 Pass. [갭] SWR-006(a)는 SWE.6 단계에서 시스템 경계 기준으로는 합격 판정에 도달하지 못했다(Fail) — OEM-FR-001 분석(Phase4 예정) 및 CycleResult의 override 상태 노출 확장 후 재검증 필요. 행 15(OEM-SR-002)와 동일 케이스 공유(ST-FUNC-0016~0017). 요구사항 커버리지: SWR-006 SWE.6까지 완료(단, (a) Fail).</t>
         </is>
       </c>
     </row>
@@ -1033,14 +1133,34 @@
           <t>ARC-0011 (IF-0017)</t>
         </is>
       </c>
-      <c r="D17" s="51" t="n"/>
-      <c r="E17" s="51" t="n"/>
-      <c r="F17" s="51" t="n"/>
-      <c r="G17" s="51" t="n"/>
-      <c r="H17" s="51" t="n"/>
-      <c r="I17" s="51" t="inlineStr">
-        <is>
-          <t>SWE.2(아키텍처 설계)까지 완료(2026-09-19) — Detailed Design/Code/SWE.4/SWE.5/SWE.6는 아직 해당 단계 아님(Phase 2 SWE.3 이후 게이트에서 채움). SWR-009(좌우 접근위험 독립 처리).</t>
+      <c r="D17" s="51" t="inlineStr">
+        <is>
+          <t>IU-0011(신규)</t>
+        </is>
+      </c>
+      <c r="E17" s="51" t="inlineStr">
+        <is>
+          <t>IU-0011: src/ngv/core/approach_risk_evaluator.py::ApproachRiskEvaluator(evaluateSide)</t>
+        </is>
+      </c>
+      <c r="F17" s="51" t="inlineStr">
+        <is>
+          <t>tests/test_approach_risk_evaluator.py(6, 좌우 무교차 testLeftTrueRightFalseActivatesOnlyLeftSuppressCandidate/testRightTrueLeftFalseActivatesOnlyRightSuppressCandidate 포함)</t>
+        </is>
+      </c>
+      <c r="G17" s="51" t="inlineStr">
+        <is>
+          <t>IT-0049~0054(좌우 4조합 FF/FT/TF/TT 및 독립성), IT-0083(전체 체인 좌우 독립 LOCK) (ENG-SWE5-002). 실행 결과: ENG-SWE5-003, 전량 Pass.</t>
+        </is>
+      </c>
+      <c r="H17" s="49" t="inlineStr">
+        <is>
+          <t>ST-FUNC-0023~0026 (ENG-SWE6-001, 좌/우 접근위험 2x2 전 조건 조합[FF/FT/TF/TT] 전수). 실행 결과: ENG-SWE6-002, 4/4 Pass.</t>
+        </is>
+      </c>
+      <c r="I17" s="49" t="inlineStr">
+        <is>
+          <t>SWE.6까지 완료(2026-09-19, sw-system-tester) — ST-FUNC-0023~0026 4/4 Pass(ENG-SWE6-002). 검증방안이 명시한 4가지 조합(FF/FT/TF/TT) 전수 실행, 좌우 완전 독립(교차 오염 없음) 확인. 요구사항 커버리지: SWR-009 SWE.6까지 완료.</t>
         </is>
       </c>
     </row>
@@ -1060,14 +1180,34 @@
           <t>ARC-0001, ARC-0005, ARC-0009, ARC-0013 (IF-0005, IF-0008, IF-0015, IF-0019)</t>
         </is>
       </c>
-      <c r="D18" s="51" t="n"/>
-      <c r="E18" s="51" t="n"/>
-      <c r="F18" s="51" t="n"/>
-      <c r="G18" s="51" t="n"/>
-      <c r="H18" s="51" t="n"/>
-      <c r="I18" s="51" t="inlineStr">
-        <is>
-          <t>SWE.2(아키텍처 설계)까지 완료(2026-09-19) — Detailed Design/Code/SWE.4/SWE.5/SWE.6는 아직 해당 단계 아님(Phase 2 SWE.3 이후 게이트에서 채움). SWR-017(화재/과온/성인탑승 확인 시 강제해제). 이유코드 카탈로그 미확정(8장 가정 12).</t>
+      <c r="D18" s="51" t="inlineStr">
+        <is>
+          <t>IU-0001, IU-0005, IU-0009, IU-0013(신규)</t>
+        </is>
+      </c>
+      <c r="E18" s="51" t="inlineStr">
+        <is>
+          <t>IU-0013: src/ngv/core/fire_overtemp_occupant_monitor.py::FireOvertempOccupantMonitor(evaluate/buildReleaseCandidate); IU-0001/IU-0005/IU-0009: 상동(행 12와 동일 갱신분 공유)</t>
+        </is>
+      </c>
+      <c r="F18" s="51" t="inlineStr">
+        <is>
+          <t>tests/test_fire_overtemp_occupant_monitor.py(5, 복수 동시 TRUE testAllThreeTrueSimultaneouslyRecordsAllReasonCodes 포함); tests/test_safety_kernel_orchestrator.py::TestSafetyKernelOrchestratorPhase2Wiring::testFireDetectedProducesReleaseOnBothDoors(종단 검증)</t>
+        </is>
+      </c>
+      <c r="G18" s="51" t="inlineStr">
+        <is>
+          <t>IT-0062~0068(IF-0019 OR 판정, 단독/복합), IT-0070(우선순위), IT-0080(IF-0015 입력검증), IT-0085~0086(전체 체인) (ENG-SWE5-002). 실행 결과: ENG-SWE5-003, 전량 Pass.</t>
+        </is>
+      </c>
+      <c r="H18" s="49" t="inlineStr">
+        <is>
+          <t>ST-FUNC-0027~0030 (ENG-SWE6-001, SWR-017(a) 동등분할 3건[fire/overtemperature/adult 단독] + SWR-017(b) 전 조건 조합 1건[3개 동시 TRUE 대표값]). 실행 결과: ENG-SWE6-002, 4/4 Pass.</t>
+        </is>
+      </c>
+      <c r="I18" s="49" t="inlineStr">
+        <is>
+          <t>SWE.6까지 완료(2026-09-19, sw-system-tester) — ST-FUNC-0027~0030 4/4 Pass(ENG-SWE6-002). 3개 입력 각각 단독 트리거 시 RELEASE 전환 및 복수 입력 동시발생 시 RELEASE 유지 확인. 적용 한계: 이유코드(입력별) 기록은 CycleResult 미노출(ledger 갭 10)로 시스템 경계에서 직접 관측 불가(하위 IT-0062~0068에서 이미 검증됨). 요구사항 커버리지: SWR-017 SWE.6까지 완료.</t>
         </is>
       </c>
     </row>
@@ -1098,7 +1238,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:F20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1458,6 +1598,134 @@
       <c r="F16" t="inlineStr">
         <is>
           <t>확인 필요(미지정)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>0.8</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>detailed-designer</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Phase 2 상세설계 — ENG-SWE3-001 v0.2/ENG-SWE3-002 갱신(IU-0010~0013 신규, IU-0001/0005/0009 갱신). Detailed Design 열(IU-NNNN) 및 Coverage 열 갱신 — SWR-005/006/007/008/009/017 대상 7개 행(OEM-SR-001/SR-002/FR-003/FR-005). ARC-0010~0013 완전 상세설계, ARC-0005 우선순위 규칙 3종 상세설계(Phase1 게이트-only 계약 대체), ARC-0001/0009 갱신.</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>초안(검토 미실시)</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>미승인</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>coding</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Phase 2 구현(TDD) — src/ngv 이하 IU-0010~0013 신규 구현(crash_monitor/approach_risk_evaluator/approach_risk_override_manager/fire_overtemp_occupant_monitor), IU-0001(validateCrashStatusField 신규, normalizeCycle 9필드 확장)/IU-0005(문별 우선순위 후보 선택으로 계약 완전 대체, 기존 NotImplementedError 검증 테스트를 Red-Green으로 교체)/IU-0009(IU-0010~0013 호출+candidateCommands 조립 단계 추가, reset() 갱신) 갱신. tests 이하 단위테스트 98건(unittest, Phase1 52건 포함 순증 46건), tests_integration/tests_system은 Phase2 신규 필드 기본값 하위호환(RawCycleInput/NormalizedSafetyInput default) 및 IU-0005/IU-0009 생성자 확장에 맞춰 it_helpers.py/st_helpers.py/test_it_step4/test_it_step6 최소 기계적 갱신(로직 변경 없음, IT-0020은 폐기된 Phase1 계약 검증을 신규 계약 검증으로 교체). 전체 회귀 스위트 154개 전량 Pass. 품질 게이트 5종(radon cc/raw, pylint duplicate-code/invalid-name) 신규/변경 파일 전부 실측 통과. Code/SWE.4/Coverage 열 갱신 (SWR-005/006/007/008/009/017 대상 7개 행 + SWR-013/021 각주). SWE.5/SWE.6는 다음 게이트.</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>초안(검토 미실시)</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>미승인</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="42" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="B19" s="42" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="C19" s="42" t="inlineStr">
+        <is>
+          <t>integration-tester</t>
+        </is>
+      </c>
+      <c r="D19" s="42" t="inlineStr">
+        <is>
+          <t>Phase 2 통합시험(SWE.5) — ENG-SWE2-001 v0.2 11장 8~14단계를 따라 IT-0044~IT-0093(50건) 신규 작성·실행, 기존 IT-0020을 IU-0005 Phase2 계약(문별 우선순위 선택)에 맞춰 갱신. ENG-SWE5-001/002/003 전부 v0.2로 갱신. 이번 통합 범위(src/ngv 전체) 함수 커버리지 100%(47/47), Call 커버리지 100%(coverage.py 직접실측 45/48 + Phase1부터 이어지는 동일한 도구 한계 3개는 recordCalls/오류주입 런타임 증거로 보완, 총 13개 아키텍처 호출관계 전부 확인). SWE.5 열(G)/Coverage 열(I) 7개 행(OEM-SR-001/SR-002/FR-003/FR-005, SWR-005/006/007/008/009/017) 갱신.</t>
+        </is>
+      </c>
+      <c r="E19" s="42" t="inlineStr">
+        <is>
+          <t>초안(검토 미실시)</t>
+        </is>
+      </c>
+      <c r="F19" s="42" t="inlineStr">
+        <is>
+          <t>미승인</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="42" t="inlineStr">
+        <is>
+          <t>1.1</t>
+        </is>
+      </c>
+      <c r="B20" s="42" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="C20" s="42" t="inlineStr">
+        <is>
+          <t>sw-system-tester</t>
+        </is>
+      </c>
+      <c r="D20" s="42" t="inlineStr">
+        <is>
+          <t>Phase 2 시스템 테스트(SWE.6, 마지막 게이트) — ENG-SWE6-001/002 v0.2 갱신(ST-FUNC-0014~0030 신규 17건: SWR-005 2건 + SWR-006 2건[10초 경계값, 1건 Fail] + SWR-007 3건[300ms 경계값 포함] + SWR-008 2건 + SWR-009 4건[좌우 독립 전 조건 조합] + SWR-017 4건). 16 Pass / 1 Fail(ST-FUNC-0016, SWR-006(a) — releaseReRequested 채널 부재[ledger 갭 7] + CycleResult 이유코드/override 상태 미노출[ledger 갭 10]로 시스템 경계에서 합격 판정 불가, 근본원인은 기지 구조적 갭). SWE.6/Coverage 열 7개 행(OEM-SR-001×2/SR-002×3/FR-003/FR-005 → SWR-005/006/007/008/009/017) 갱신 — 이 6개 요구사항의 추적 사슬이 SWE.6까지 완성됨(단, SWR-006(a)는 Fail로 명시). Phase 2 전체 게이트(SWE.1~SWE.6) 완료.</t>
+        </is>
+      </c>
+      <c r="E20" s="42" t="inlineStr">
+        <is>
+          <t>초안(검토 미실시)</t>
+        </is>
+      </c>
+      <c r="F20" s="42" t="inlineStr">
+        <is>
+          <t>미승인</t>
         </is>
       </c>
     </row>

--- a/Deliverables/Engineering/Traceability/ENG-TRC-001_양방향 요구사항 추적 매트릭스.xlsx
+++ b/Deliverables/Engineering/Traceability/ENG-TRC-001_양방향 요구사항 추적 매트릭스.xlsx
@@ -211,7 +211,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -312,6 +312,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -616,7 +619,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I11"/>
+  <dimension ref="A1:I18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -701,7 +704,7 @@
       </c>
       <c r="F4" s="9" t="inlineStr">
         <is>
-          <t>v0.1 (Draft) — Phase 1 최초 작성</t>
+          <t>v0.2 (Draft) — Phase 2(안전 긴급 대응) 갱신, Phase 1 내용 유지</t>
         </is>
       </c>
       <c r="G4" s="9" t="str"/>
@@ -808,12 +811,12 @@
       </c>
       <c r="E10" s="42" t="inlineStr">
         <is>
-          <t>IU-0001: src/ngv/adapters/input_validation_adapter.py::InputValidationAdapter (validateTimestampField/validateBooleanField/applySensorFaultFailSafe/normalizeCycle/handleCycle); IU-0002: src/ngv/core/freshness_monitor.py::FreshnessMonitor(evaluate/reset); IU-0003: src/ngv/core/state_manager.py::StateManager(evaluate/reset); IU-0009: src/ngv/app/safety_kernel_orchestrator.py::SafetyKernelOrchestrator(evaluateCycle/reset)</t>
+          <t>IU-0001: src/ngv/adapters/input_validation_adapter.py::InputValidationAdapter (validateTimestampField/validateBooleanField/applySensorFaultFailSafe/normalizeCycle/handleCycle); IU-0002: src/ngv/core/freshness_monitor.py::FreshnessMonitor(evaluate/reset); IU-0003: src/ngv/core/state_manager.py::StateManager(evaluate/reset); IU-0009: src/ngv/app/safety_kernel_orchestrator.py::SafetyKernelOrchestrator(evaluateCycle/reset)  [Phase2 갱신 각주(2026-09-19)] IU-0001.normalizeCycle()은 9필드로 확장되었으나 SWR-013(a)/(b) 판정 로직 자체는 변경 없음(Phase2 6필드는 별도 하류 IU-0010~0013이 소비). IU-0009.evaluateCycle()은 IU-0010~0013 호출과 candidateCommands 조립 단계가 추가되었으나 freshness/state 판정 순서와 SWR-013 관련 동작은 동일하게 유지됨. 회귀 확인: tests/test_input_validation_adapter.py::TestNormalizeCycle(신규 2건 포함 총 9건), tests/test_safety_kernel_orchestrator.py 전량 Pass(품질 게이트 통과, 행 12~18 Coverage 참조).</t>
         </is>
       </c>
       <c r="F10" s="42" t="inlineStr">
         <is>
-          <t>tests/test_input_validation_adapter.py; tests/test_freshness_monitor.py; tests/test_state_manager.py; tests/test_safety_kernel_orchestrator.py (unittest, 42 테스트, 전량 Positive+Negative — test-annotation.md 형식 준수)</t>
+          <t>tests/test_input_validation_adapter.py; tests/test_freshness_monitor.py; tests/test_state_manager.py; tests/test_safety_kernel_orchestrator.py (unittest, 42 테스트, 전량 Positive+Negative — test-annotation.md 형식 준수) tests/test_input_validation_adapter.py; tests/test_safety_kernel_orchestrator.py(Phase2 갱신 후 회귀 없음, 2026-09-19 재확인)</t>
         </is>
       </c>
       <c r="G10" s="42" t="inlineStr">
@@ -855,12 +858,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>IU-0003: src/ngv/core/state_manager.py::StateManager(evaluate/reset); IU-0004: src/ngv/core/output_hold_actuator.py::OutputHoldActuator(confirm/reset/getLastConfirmedOutput); IU-0005: src/ngv/core/command_arbiter.py::CommandArbiter(arbitrate) [최소구현: 게이트만, Phase1]; IU-0007: src/ngv/adapters/notification_adapter.py::NotificationAdapter(publishWarning) [최소구현: 패스스루]; IU-0009: src/ngv/app/safety_kernel_orchestrator.py::SafetyKernelOrchestrator(evaluateCycle/reset)</t>
+          <t>IU-0003: src/ngv/core/state_manager.py::StateManager(evaluate/reset); IU-0004: src/ngv/core/output_hold_actuator.py::OutputHoldActuator(confirm/reset/getLastConfirmedOutput); IU-0005: src/ngv/core/command_arbiter.py::CommandArbiter(arbitrate) [최소구현: 게이트만, Phase1]; IU-0007: src/ngv/adapters/notification_adapter.py::NotificationAdapter(publishWarning) [최소구현: 패스스루]; IU-0009: src/ngv/app/safety_kernel_orchestrator.py::SafetyKernelOrchestrator(evaluateCycle/reset)  [Phase2 갱신 각주(2026-09-19)] IU-0005.arbitrate()는 5.2절에 따라 "candidateCommands 비어있지 않으면 NotImplementedError" 계약을 완전히 폐기하고 문(door)별 최소-priority 후보 선택 알고리즘(selectForDoor(), 동일 priority 충돌 시 ValueError)으로 대체됨 — 하위호환 아님. SWR-021(a)/(b) 게이트(FAULT/inputInvalid 최우선) 자체는 변경 없이 유지. 기존 tests/test_command_arbiter.py의 NotImplementedError 검증 테스트는 새 계약을 검증하도록 전면 재작성됨(10건, TDD Red-Green 확인). IU-0007(패스스루)은 Phase2 이유코드 미발행으로 변경 없음.</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>tests/test_state_manager.py; tests/test_output_hold_actuator.py; tests/test_command_arbiter.py; tests/test_notification_adapter.py; tests/test_safety_kernel_orchestrator.py (unittest, IU-0005/0007은 Phase1 최소계약 범위만 검증)</t>
+          <t>tests/test_state_manager.py; tests/test_output_hold_actuator.py; tests/test_command_arbiter.py; tests/test_notification_adapter.py; tests/test_safety_kernel_orchestrator.py (unittest, IU-0005/0007은 Phase1 최소계약 범위만 검증) tests/test_command_arbiter.py(전면 재작성, 10건); tests/test_safety_kernel_orchestrator.py(Phase2 갱신 후 회귀 없음)</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -876,6 +879,335 @@
       <c r="I11" s="50" t="inlineStr">
         <is>
           <t>SWE.6까지 완료(2026-09-18) — ST-FUNC-0009~0013 5/5 Pass(ENG-SWE6-002, ST-FUNC-0009는 SWR-013(b)/SWR-021(b) 제안 케이스로 두 행에 공유 표기). SWR-021(a) fail-freeze(첫 주기+지속) 검증, SWR-021(b) FAULT 전이+경고코드(첫 전이+지속) 검증. 적용 한계: 합격기준 비고의 "동일 주기 신규 명령 미반영" 시나리오는 Phase1에 후보 명령(candidateCommands) 채널 자체가 없어(항상 빈 리스트) 시험 대상에서 구조적으로 제외 — 이후 Phase에서 명령 채널이 추가되면 재검증 필요. DEGRADED/FAULT 상태 간 관계(복귀조건 등)는 요구사항 원문 미정(8장 가정 3)이라 시험 대상에서 제외.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="34" customHeight="1">
+      <c r="A12" s="51" t="inlineStr">
+        <is>
+          <t>OEM-SR-001</t>
+        </is>
+      </c>
+      <c r="B12" s="51" t="inlineStr">
+        <is>
+          <t>SWR-007</t>
+        </is>
+      </c>
+      <c r="C12" s="51" t="inlineStr">
+        <is>
+          <t>ARC-0001, ARC-0004, ARC-0005, ARC-0009, ARC-0010 (IF-0005, IF-0008, IF-0009, IF-0013, IF-0016)</t>
+        </is>
+      </c>
+      <c r="D12" s="51" t="inlineStr">
+        <is>
+          <t>IU-0001, IU-0004, IU-0005, IU-0009, IU-0010(신규)</t>
+        </is>
+      </c>
+      <c r="E12" s="51" t="inlineStr">
+        <is>
+          <t>IU-0010: src/ngv/core/crash_monitor.py::CrashMonitor(evaluate); IU-0001: src/ngv/adapters/input_validation_adapter.py::InputValidationAdapter(validateCrashStatusField[신규]/normalizeCycle[갱신, 9필드]); IU-0005: src/ngv/core/command_arbiter.py::CommandArbiter(arbitrate/selectForDoor)[갱신, 계약 대체]; IU-0004: src/ngv/core/output_hold_actuator.py::OutputHoldActuator(confirm)[변경 없음]; IU-0009: src/ngv/app/safety_kernel_orchestrator.py::SafetyKernelOrchestrator(evaluateCycle/evaluatePhase2Candidates/assembleCandidateCommands)[갱신]</t>
+        </is>
+      </c>
+      <c r="F12" s="51" t="inlineStr">
+        <is>
+          <t>tests/test_crash_monitor.py(5, CONFIRMED→RELEASE 후보/priority=1 포함); tests/test_input_validation_adapter.py::TestValidateCrashStatusField(5); tests/test_command_arbiter.py(10, 전면 재작성 — 5.2절 계약 대체 반영); tests/test_safety_kernel_orchestrator.py::TestSafetyKernelOrchestratorPhase2Wiring::testCrashConfirmedProducesReleaseOnBothDoors(종단 검증, 300ms 예산 여유분석은 6.1b절 근거로 별도 타이밍 시험 불필요)</t>
+        </is>
+      </c>
+      <c r="G12" s="51" t="inlineStr">
+        <is>
+          <t>IT-0044, IT-0046~IT-0048(IF-0016 판정), IT-0069, IT-0073, IT-0082, IT-0086~0089, IT-0092(우선순위 중재·게이트·전체 체인), IT-0075~0078, IT-0093(IF-0013 입력검증) (ENG-SWE5-002). 실행 결과: ENG-SWE5-003, 전량 Pass.</t>
+        </is>
+      </c>
+      <c r="H12" s="49" t="inlineStr">
+        <is>
+          <t>ST-FUNC-0018~0020 (ENG-SWE6-001, SWR-007(a) 경계값분석 1건[300ms 예산, 평가주기 간격 스트레스] + 결정표기반 시험 1건[crash vs 접근위험 우선순위] + 상태전이 테스트 1건[RELEASE 지속]). 실행 결과: ENG-SWE6-002(Verification Results), 3/3 Pass.</t>
+        </is>
+      </c>
+      <c r="I12" s="49" t="inlineStr">
+        <is>
+          <t>SWE.6까지 완료(2026-09-19, sw-system-tester) — ST-FUNC-0018~0020 3/3 Pass(ENG-SWE6-002). SWR-007(a) 300ms 예산(즉시 반영, crash_monitor에 elapsed-time 게이트 없음 확인) 및 최우선 순위(crash&gt;접근위험) 검증, SWR-007(b) RELEASE 지속(경쟁 조건 등장 후에도 유지) 검증. 적용 한계: 복수 조건 동시발생의 전수 조합은 아님(3장 우선순위 관계로 도출 가능한 대표 시나리오만 검증). 요구사항 커버리지: SWR-007 SWE.6까지 완료.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="34" customHeight="1">
+      <c r="A13" s="51" t="inlineStr">
+        <is>
+          <t>OEM-SR-001</t>
+        </is>
+      </c>
+      <c r="B13" s="51" t="inlineStr">
+        <is>
+          <t>SWR-008</t>
+        </is>
+      </c>
+      <c r="C13" s="51" t="inlineStr">
+        <is>
+          <t>ARC-0010 (IF-0016)</t>
+        </is>
+      </c>
+      <c r="D13" s="51" t="inlineStr">
+        <is>
+          <t>IU-0010(신규)</t>
+        </is>
+      </c>
+      <c r="E13" s="51" t="inlineStr">
+        <is>
+          <t>IU-0010: src/ngv/core/crash_monitor.py::CrashMonitor(evaluate)</t>
+        </is>
+      </c>
+      <c r="F13" s="51" t="inlineStr">
+        <is>
+          <t>tests/test_crash_monitor.py::TestCrashMonitorEvaluate::testPendingStatusAppliesHoldWithoutReleaseCandidate(PENDING→releaseCandidate=None/pendingHoldApplied=True)</t>
+        </is>
+      </c>
+      <c r="G13" s="51" t="inlineStr">
+        <is>
+          <t>IT-0045(PENDING 보류 판정, ENG-SWE5-002). 실행 결과: ENG-SWE5-003, Pass.</t>
+        </is>
+      </c>
+      <c r="H13" s="49" t="inlineStr">
+        <is>
+          <t>ST-FUNC-0021~0022 (ENG-SWE6-001, SWR-008 동등분할 1건[PENDING 클래스] + 요구사항 기반 시험 1건[SWR-008/SWR-017 상호작용]). 실행 결과: ENG-SWE6-002, 2/2 Pass.</t>
+        </is>
+      </c>
+      <c r="I13" s="49" t="inlineStr">
+        <is>
+          <t>SWE.6까지 완료(2026-09-19, sw-system-tester) — ST-FUNC-0021~0022 2/2 Pass(ENG-SWE6-002). PENDING이 긴급해제를 조기 개시하지 않고 다른 SWR(SWR-017)의 독립 로직도 차단하지 않음을 확인. 적용 한계: 본 요구사항 자체가 OEM 원문 비명시 추론 요구사항(ENG-SWE1-001 8장 가정 6, OEM-A 확인 필요) — 시스템 시험도 이 추론을 그대로 전제로 함. 요구사항 커버리지: SWR-008 SWE.6까지 완료.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="34" customHeight="1">
+      <c r="A14" s="51" t="inlineStr">
+        <is>
+          <t>OEM-SR-002</t>
+        </is>
+      </c>
+      <c r="B14" s="51" t="inlineStr">
+        <is>
+          <t>SWR-005</t>
+        </is>
+      </c>
+      <c r="C14" s="51" t="inlineStr">
+        <is>
+          <t>ARC-0001, ARC-0005, ARC-0009, ARC-0011 (IF-0005, IF-0008, IF-0014, IF-0017)</t>
+        </is>
+      </c>
+      <c r="D14" s="51" t="inlineStr">
+        <is>
+          <t>IU-0001, IU-0005, IU-0009, IU-0011(신규)</t>
+        </is>
+      </c>
+      <c r="E14" s="51" t="inlineStr">
+        <is>
+          <t>IU-0011: src/ngv/core/approach_risk_evaluator.py::ApproachRiskEvaluator(evaluate/evaluateSide); IU-0001/IU-0005/IU-0009: 상동(행 12와 동일 갱신분 공유)</t>
+        </is>
+      </c>
+      <c r="F14" s="51" t="inlineStr">
+        <is>
+          <t>tests/test_approach_risk_evaluator.py(6, SWR-009 4조합 FF/FT/TF/TT 전수 포함); tests/test_safety_kernel_orchestrator.py::TestSafetyKernelOrchestratorPhase2Wiring::testLeftApproachRiskLocksOnlyLeftDoor(종단 검증)</t>
+        </is>
+      </c>
+      <c r="G14" s="51" t="inlineStr">
+        <is>
+          <t>IT-0049~0054(IF-0017 억제 판정), IT-0070~0071(우선순위·문별 독립성), IT-0079(IF-0014 입력검증), IT-0083(전체 체인) (ENG-SWE5-002). 실행 결과: ENG-SWE5-003, 전량 Pass.</t>
+        </is>
+      </c>
+      <c r="H14" s="49" t="inlineStr">
+        <is>
+          <t>ST-FUNC-0014~0015 (ENG-SWE6-001, SWR-005(a) 요구사항 기반 시험 1건[단일 도어 LOCK] + SWR-005(b) 결정표기반/오류추측 1건[경쟁 RELEASE 후보 억제]). SWR-009 4조합(ST-FUNC-0023~0026)의 TF/FT 케이스도 SWR-005(a) 관측을 겸함. 실행 결과: ENG-SWE6-002, 2/2 Pass(겸용 케이스 포함 시 4/4).</t>
+        </is>
+      </c>
+      <c r="I14" s="49" t="inlineStr">
+        <is>
+          <t>SWE.6까지 완료(2026-09-19, sw-system-tester) — ST-FUNC-0014~0015 2/2 Pass(ENG-SWE6-002). 접근위험 TRUE 시 LOCK 전환(a) 및 경쟁 RELEASE 후보 대비 억제 유지(b, 우선순위 기반 간접 검증) 확인. 적용 한계: 원문의 "해제 요청"은 통상 운전자 수동명령(OEM-FR-001)을 뜻하나 이 채널은 Phase2 범위 밖(1.3절)이라 직접 재현 불가 — 경쟁 RELEASE 후보(SWR-017)로 대체 검증. 이유코드(억제 사유) 기록은 CycleResult 미노출(ledger 갭 10)로 시스템 경계에서 직접 관측 불가(하위 IT-0049~0054/0079/0083에서 이미 검증됨). 요구사항 커버리지: SWR-005 SWE.6까지 완료.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="34" customHeight="1">
+      <c r="A15" s="51" t="inlineStr">
+        <is>
+          <t>OEM-SR-002</t>
+        </is>
+      </c>
+      <c r="B15" s="51" t="inlineStr">
+        <is>
+          <t>SWR-006</t>
+        </is>
+      </c>
+      <c r="C15" s="51" t="inlineStr">
+        <is>
+          <t>ARC-0005, ARC-0009, ARC-0011, ARC-0012 (IF-0008, IF-0017, IF-0018)</t>
+        </is>
+      </c>
+      <c r="D15" s="51" t="inlineStr">
+        <is>
+          <t>IU-0005, IU-0009, IU-0011, IU-0012(신규)</t>
+        </is>
+      </c>
+      <c r="E15" s="51" t="inlineStr">
+        <is>
+          <t>IU-0011: src/ngv/core/approach_risk_evaluator.py::ApproachRiskEvaluator(evaluate); IU-0012: src/ngv/core/approach_risk_override_manager.py::ApproachRiskOverrideManager(decide/decideSide/reset)[유일한 상태 보유]; IU-0009: src/ngv/app/safety_kernel_orchestrator.py::SafetyKernelOrchestrator(evaluatePhase2Candidates/assembleCandidateCommands/reset)</t>
+        </is>
+      </c>
+      <c r="F15" s="51" t="inlineStr">
+        <is>
+          <t>tests/test_approach_risk_override_manager.py(8, 10.0s/10.1s 경계값분석 포함 — SWR-006(a)/(b) 문언 경계, 리셋 규칙 testResetClearsSuppressionTimerEvenWhileRiskStaysActive 포함); tests/test_safety_kernel_orchestrator.py::TestSafetyKernelOrchestratorReset::testResetClearsOverrideManagerSuppressionTimer; tests/test_safety_kernel_orchestrator.py::TestSafetyKernelOrchestratorAssembleCandidateCommands::testExcludesLeftSuppressCandidateWhenLeftOverrideActive(override의 LOCK 후보 철회, 비강제 확인)</t>
+        </is>
+      </c>
+      <c r="G15" s="51" t="inlineStr">
+        <is>
+          <t>IT-0055~0061(IF-0018 override 판정, 10s 경계값·타이머 리셋·좌우 독립), IT-0084(전체 체인 placeholder 한계 실증) (ENG-SWE5-002). 실행 결과: ENG-SWE5-003, 전량 Pass.</t>
+        </is>
+      </c>
+      <c r="H15" s="49" t="inlineStr">
+        <is>
+          <t>ST-FUNC-0016~0017 (ENG-SWE6-001, SWR-006(a) 경계값분석 1건[10초 이내 경계, elapsed=10.000s] + SWR-006(b) 경계값분석 1건[10초 초과 경계, elapsed=10.100s]). 실행 결과: ENG-SWE6-002, 1/2 Pass(ST-FUNC-0016 Fail).</t>
+        </is>
+      </c>
+      <c r="I15" s="49" t="inlineStr">
+        <is>
+          <t>SWE.6까지 완료(2026-09-19, sw-system-tester) — ST-FUNC-0016~0017 1/2 Pass(ENG-SWE6-002). ST-FUNC-0016(10초 이내 override 생성, SWR-006a)은 Fail — releaseReRequested 채널이 원시 입력에 없고(OEM-FR-001 미분석, ledger 갭 7) CycleResult가 override 상태/이유코드를 노출하지 않아(ledger 갭 10) 시스템 경계에서 SWR-006(a) 성립을 확인할 수 없음(근본원인은 기지 구조적 갭이며, IT-0084가 통합 수준에서 이미 이 한계를 문서화). ST-FUNC-0017(10초 초과, 억제 유지, SWR-006b)은 Pass. [갭] SWR-006(a)는 SWE.6 단계에서 시스템 경계 기준으로는 합격 판정에 도달하지 못했다(Fail) — OEM-FR-001 분석(Phase4 예정) 및 CycleResult의 override 상태 노출 확장 후 재검증 필요. 요구사항 커버리지: SWR-006 SWE.6까지 완료(단, (a) Fail).</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="34" customHeight="1">
+      <c r="A16" s="51" t="inlineStr">
+        <is>
+          <t>OEM-FR-003</t>
+        </is>
+      </c>
+      <c r="B16" s="51" t="inlineStr">
+        <is>
+          <t>SWR-006</t>
+        </is>
+      </c>
+      <c r="C16" s="51" t="inlineStr">
+        <is>
+          <t>ARC-0005, ARC-0009, ARC-0011, ARC-0012 (IF-0008, IF-0017, IF-0018)</t>
+        </is>
+      </c>
+      <c r="D16" s="51" t="inlineStr">
+        <is>
+          <t>IU-0005, IU-0009, IU-0011, IU-0012(신규)</t>
+        </is>
+      </c>
+      <c r="E16" s="51" t="inlineStr">
+        <is>
+          <t>IU-0011: src/ngv/core/approach_risk_evaluator.py::ApproachRiskEvaluator(evaluate); IU-0012: src/ngv/core/approach_risk_override_manager.py::ApproachRiskOverrideManager(decide/decideSide/reset)[유일한 상태 보유]; IU-0009: src/ngv/app/safety_kernel_orchestrator.py::SafetyKernelOrchestrator(evaluatePhase2Candidates/assembleCandidateCommands/reset)</t>
+        </is>
+      </c>
+      <c r="F16" s="51" t="inlineStr">
+        <is>
+          <t>tests/test_approach_risk_override_manager.py(8, 10.0s/10.1s 경계값분석 포함 — SWR-006(a)/(b) 문언 경계, 리셋 규칙 testResetClearsSuppressionTimerEvenWhileRiskStaysActive 포함); tests/test_safety_kernel_orchestrator.py::TestSafetyKernelOrchestratorReset::testResetClearsOverrideManagerSuppressionTimer; tests/test_safety_kernel_orchestrator.py::TestSafetyKernelOrchestratorAssembleCandidateCommands::testExcludesLeftSuppressCandidateWhenLeftOverrideActive(override의 LOCK 후보 철회, 비강제 확인)</t>
+        </is>
+      </c>
+      <c r="G16" s="51" t="inlineStr">
+        <is>
+          <t>IT-0055~0061, IT-0084 (행 15와 동일 공유, ENG-SWE5-002). 실행 결과: ENG-SWE5-003, 전량 Pass.</t>
+        </is>
+      </c>
+      <c r="H16" s="49" t="inlineStr">
+        <is>
+          <t>ST-FUNC-0016~0017 (ENG-SWE6-001, SWR-006(a) 경계값분석 1건[10초 이내 경계, elapsed=10.000s] + SWR-006(b) 경계값분석 1건[10초 초과 경계, elapsed=10.100s]). 실행 결과: ENG-SWE6-002, 1/2 Pass(ST-FUNC-0016 Fail).</t>
+        </is>
+      </c>
+      <c r="I16" s="49" t="inlineStr">
+        <is>
+          <t>SWE.6까지 완료(2026-09-19, sw-system-tester) — ST-FUNC-0016~0017 1/2 Pass(ENG-SWE6-002). ST-FUNC-0016(10초 이내 override 생성, SWR-006a)은 Fail — releaseReRequested 채널이 원시 입력에 없고(OEM-FR-001 미분석, ledger 갭 7) CycleResult가 override 상태/이유코드를 노출하지 않아(ledger 갭 10) 시스템 경계에서 SWR-006(a) 성립을 확인할 수 없음(근본원인은 기지 구조적 갭이며, IT-0084가 통합 수준에서 이미 이 한계를 문서화). ST-FUNC-0017(10초 초과, 억제 유지, SWR-006b)은 Pass. [갭] SWR-006(a)는 SWE.6 단계에서 시스템 경계 기준으로는 합격 판정에 도달하지 못했다(Fail) — OEM-FR-001 분석(Phase4 예정) 및 CycleResult의 override 상태 노출 확장 후 재검증 필요. 행 15(OEM-SR-002)와 동일 케이스 공유(ST-FUNC-0016~0017). 요구사항 커버리지: SWR-006 SWE.6까지 완료(단, (a) Fail).</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="34" customHeight="1">
+      <c r="A17" s="51" t="inlineStr">
+        <is>
+          <t>OEM-SR-002</t>
+        </is>
+      </c>
+      <c r="B17" s="51" t="inlineStr">
+        <is>
+          <t>SWR-009</t>
+        </is>
+      </c>
+      <c r="C17" s="51" t="inlineStr">
+        <is>
+          <t>ARC-0011 (IF-0017)</t>
+        </is>
+      </c>
+      <c r="D17" s="51" t="inlineStr">
+        <is>
+          <t>IU-0011(신규)</t>
+        </is>
+      </c>
+      <c r="E17" s="51" t="inlineStr">
+        <is>
+          <t>IU-0011: src/ngv/core/approach_risk_evaluator.py::ApproachRiskEvaluator(evaluateSide)</t>
+        </is>
+      </c>
+      <c r="F17" s="51" t="inlineStr">
+        <is>
+          <t>tests/test_approach_risk_evaluator.py(6, 좌우 무교차 testLeftTrueRightFalseActivatesOnlyLeftSuppressCandidate/testRightTrueLeftFalseActivatesOnlyRightSuppressCandidate 포함)</t>
+        </is>
+      </c>
+      <c r="G17" s="51" t="inlineStr">
+        <is>
+          <t>IT-0049~0054(좌우 4조합 FF/FT/TF/TT 및 독립성), IT-0083(전체 체인 좌우 독립 LOCK) (ENG-SWE5-002). 실행 결과: ENG-SWE5-003, 전량 Pass.</t>
+        </is>
+      </c>
+      <c r="H17" s="49" t="inlineStr">
+        <is>
+          <t>ST-FUNC-0023~0026 (ENG-SWE6-001, 좌/우 접근위험 2x2 전 조건 조합[FF/FT/TF/TT] 전수). 실행 결과: ENG-SWE6-002, 4/4 Pass.</t>
+        </is>
+      </c>
+      <c r="I17" s="49" t="inlineStr">
+        <is>
+          <t>SWE.6까지 완료(2026-09-19, sw-system-tester) — ST-FUNC-0023~0026 4/4 Pass(ENG-SWE6-002). 검증방안이 명시한 4가지 조합(FF/FT/TF/TT) 전수 실행, 좌우 완전 독립(교차 오염 없음) 확인. 요구사항 커버리지: SWR-009 SWE.6까지 완료.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="34" customHeight="1">
+      <c r="A18" s="51" t="inlineStr">
+        <is>
+          <t>OEM-FR-005</t>
+        </is>
+      </c>
+      <c r="B18" s="51" t="inlineStr">
+        <is>
+          <t>SWR-017</t>
+        </is>
+      </c>
+      <c r="C18" s="51" t="inlineStr">
+        <is>
+          <t>ARC-0001, ARC-0005, ARC-0009, ARC-0013 (IF-0005, IF-0008, IF-0015, IF-0019)</t>
+        </is>
+      </c>
+      <c r="D18" s="51" t="inlineStr">
+        <is>
+          <t>IU-0001, IU-0005, IU-0009, IU-0013(신규)</t>
+        </is>
+      </c>
+      <c r="E18" s="51" t="inlineStr">
+        <is>
+          <t>IU-0013: src/ngv/core/fire_overtemp_occupant_monitor.py::FireOvertempOccupantMonitor(evaluate/buildReleaseCandidate); IU-0001/IU-0005/IU-0009: 상동(행 12와 동일 갱신분 공유)</t>
+        </is>
+      </c>
+      <c r="F18" s="51" t="inlineStr">
+        <is>
+          <t>tests/test_fire_overtemp_occupant_monitor.py(5, 복수 동시 TRUE testAllThreeTrueSimultaneouslyRecordsAllReasonCodes 포함); tests/test_safety_kernel_orchestrator.py::TestSafetyKernelOrchestratorPhase2Wiring::testFireDetectedProducesReleaseOnBothDoors(종단 검증)</t>
+        </is>
+      </c>
+      <c r="G18" s="51" t="inlineStr">
+        <is>
+          <t>IT-0062~0068(IF-0019 OR 판정, 단독/복합), IT-0070(우선순위), IT-0080(IF-0015 입력검증), IT-0085~0086(전체 체인) (ENG-SWE5-002). 실행 결과: ENG-SWE5-003, 전량 Pass.</t>
+        </is>
+      </c>
+      <c r="H18" s="49" t="inlineStr">
+        <is>
+          <t>ST-FUNC-0027~0030 (ENG-SWE6-001, SWR-017(a) 동등분할 3건[fire/overtemperature/adult 단독] + SWR-017(b) 전 조건 조합 1건[3개 동시 TRUE 대표값]). 실행 결과: ENG-SWE6-002, 4/4 Pass.</t>
+        </is>
+      </c>
+      <c r="I18" s="49" t="inlineStr">
+        <is>
+          <t>SWE.6까지 완료(2026-09-19, sw-system-tester) — ST-FUNC-0027~0030 4/4 Pass(ENG-SWE6-002). 3개 입력 각각 단독 트리거 시 RELEASE 전환 및 복수 입력 동시발생 시 RELEASE 유지 확인. 적용 한계: 이유코드(입력별) 기록은 CycleResult 미노출(ledger 갭 10)로 시스템 경계에서 직접 관측 불가(하위 IT-0062~0068에서 이미 검증됨). 요구사항 커버리지: SWR-017 SWE.6까지 완료.</t>
         </is>
       </c>
     </row>
@@ -906,7 +1238,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:F20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1200,6 +1532,198 @@
         </is>
       </c>
       <c r="F14" s="50" t="inlineStr">
+        <is>
+          <t>미승인</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>0.6</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>requirements-analyst</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Phase 2 갱신 — OEM-SR-001(→SWR-007/008), OEM-SR-002(→SWR-005/006/009), OEM-FR-003(→SWR-006, OEM-SR-002와 공유), OEM-FR-005(→SWR-017)의 Upper Req/SW Req 행 7건 추가 (ENG-SWE1-001 Phase 2 갱신과 함께).</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>초안(검토 미실시)</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>미승인</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>0.7</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>orchestrator (session)</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>아키텍처 서브에이전트가 중단된 지점(Architecture 열 미기재)을 ENG-SWE2-001 12/14장 매핑 그대로 완성</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>초안(검토 미실시)</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>확인 필요(미지정)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>0.8</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>detailed-designer</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Phase 2 상세설계 — ENG-SWE3-001 v0.2/ENG-SWE3-002 갱신(IU-0010~0013 신규, IU-0001/0005/0009 갱신). Detailed Design 열(IU-NNNN) 및 Coverage 열 갱신 — SWR-005/006/007/008/009/017 대상 7개 행(OEM-SR-001/SR-002/FR-003/FR-005). ARC-0010~0013 완전 상세설계, ARC-0005 우선순위 규칙 3종 상세설계(Phase1 게이트-only 계약 대체), ARC-0001/0009 갱신.</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>초안(검토 미실시)</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>미승인</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>coding</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Phase 2 구현(TDD) — src/ngv 이하 IU-0010~0013 신규 구현(crash_monitor/approach_risk_evaluator/approach_risk_override_manager/fire_overtemp_occupant_monitor), IU-0001(validateCrashStatusField 신규, normalizeCycle 9필드 확장)/IU-0005(문별 우선순위 후보 선택으로 계약 완전 대체, 기존 NotImplementedError 검증 테스트를 Red-Green으로 교체)/IU-0009(IU-0010~0013 호출+candidateCommands 조립 단계 추가, reset() 갱신) 갱신. tests 이하 단위테스트 98건(unittest, Phase1 52건 포함 순증 46건), tests_integration/tests_system은 Phase2 신규 필드 기본값 하위호환(RawCycleInput/NormalizedSafetyInput default) 및 IU-0005/IU-0009 생성자 확장에 맞춰 it_helpers.py/st_helpers.py/test_it_step4/test_it_step6 최소 기계적 갱신(로직 변경 없음, IT-0020은 폐기된 Phase1 계약 검증을 신규 계약 검증으로 교체). 전체 회귀 스위트 154개 전량 Pass. 품질 게이트 5종(radon cc/raw, pylint duplicate-code/invalid-name) 신규/변경 파일 전부 실측 통과. Code/SWE.4/Coverage 열 갱신 (SWR-005/006/007/008/009/017 대상 7개 행 + SWR-013/021 각주). SWE.5/SWE.6는 다음 게이트.</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>초안(검토 미실시)</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>미승인</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="42" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="B19" s="42" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="C19" s="42" t="inlineStr">
+        <is>
+          <t>integration-tester</t>
+        </is>
+      </c>
+      <c r="D19" s="42" t="inlineStr">
+        <is>
+          <t>Phase 2 통합시험(SWE.5) — ENG-SWE2-001 v0.2 11장 8~14단계를 따라 IT-0044~IT-0093(50건) 신규 작성·실행, 기존 IT-0020을 IU-0005 Phase2 계약(문별 우선순위 선택)에 맞춰 갱신. ENG-SWE5-001/002/003 전부 v0.2로 갱신. 이번 통합 범위(src/ngv 전체) 함수 커버리지 100%(47/47), Call 커버리지 100%(coverage.py 직접실측 45/48 + Phase1부터 이어지는 동일한 도구 한계 3개는 recordCalls/오류주입 런타임 증거로 보완, 총 13개 아키텍처 호출관계 전부 확인). SWE.5 열(G)/Coverage 열(I) 7개 행(OEM-SR-001/SR-002/FR-003/FR-005, SWR-005/006/007/008/009/017) 갱신.</t>
+        </is>
+      </c>
+      <c r="E19" s="42" t="inlineStr">
+        <is>
+          <t>초안(검토 미실시)</t>
+        </is>
+      </c>
+      <c r="F19" s="42" t="inlineStr">
+        <is>
+          <t>미승인</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="42" t="inlineStr">
+        <is>
+          <t>1.1</t>
+        </is>
+      </c>
+      <c r="B20" s="42" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="C20" s="42" t="inlineStr">
+        <is>
+          <t>sw-system-tester</t>
+        </is>
+      </c>
+      <c r="D20" s="42" t="inlineStr">
+        <is>
+          <t>Phase 2 시스템 테스트(SWE.6, 마지막 게이트) — ENG-SWE6-001/002 v0.2 갱신(ST-FUNC-0014~0030 신규 17건: SWR-005 2건 + SWR-006 2건[10초 경계값, 1건 Fail] + SWR-007 3건[300ms 경계값 포함] + SWR-008 2건 + SWR-009 4건[좌우 독립 전 조건 조합] + SWR-017 4건). 16 Pass / 1 Fail(ST-FUNC-0016, SWR-006(a) — releaseReRequested 채널 부재[ledger 갭 7] + CycleResult 이유코드/override 상태 미노출[ledger 갭 10]로 시스템 경계에서 합격 판정 불가, 근본원인은 기지 구조적 갭). SWE.6/Coverage 열 7개 행(OEM-SR-001×2/SR-002×3/FR-003/FR-005 → SWR-005/006/007/008/009/017) 갱신 — 이 6개 요구사항의 추적 사슬이 SWE.6까지 완성됨(단, SWR-006(a)는 Fail로 명시). Phase 2 전체 게이트(SWE.1~SWE.6) 완료.</t>
+        </is>
+      </c>
+      <c r="E20" s="42" t="inlineStr">
+        <is>
+          <t>초안(검토 미실시)</t>
+        </is>
+      </c>
+      <c r="F20" s="42" t="inlineStr">
         <is>
           <t>미승인</t>
         </is>

--- a/Deliverables/Engineering/Traceability/ENG-TRC-001_양방향 요구사항 추적 매트릭스.xlsx
+++ b/Deliverables/Engineering/Traceability/ENG-TRC-001_양방향 요구사항 추적 매트릭스.xlsx
@@ -619,7 +619,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I18"/>
+  <dimension ref="A1:I21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -704,7 +704,7 @@
       </c>
       <c r="F4" s="9" t="inlineStr">
         <is>
-          <t>v0.2 (Draft) — Phase 2(안전 긴급 대응) 갱신, Phase 1 내용 유지</t>
+          <t>v0.3 (Draft) — Phase 3(자동주행잠금/ISOFIX강제잠금/ignition-off해제) 갱신, Phase 1/2 내용 유지</t>
         </is>
       </c>
       <c r="G4" s="9" t="str"/>
@@ -1208,6 +1208,75 @@
       <c r="I18" s="49" t="inlineStr">
         <is>
           <t>SWE.6까지 완료(2026-09-19, sw-system-tester) — ST-FUNC-0027~0030 4/4 Pass(ENG-SWE6-002). 3개 입력 각각 단독 트리거 시 RELEASE 전환 및 복수 입력 동시발생 시 RELEASE 유지 확인. 적용 한계: 이유코드(입력별) 기록은 CycleResult 미노출(ledger 갭 10)로 시스템 경계에서 직접 관측 불가(하위 IT-0062~0068에서 이미 검증됨). 요구사항 커버리지: SWR-017 SWE.6까지 완료.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="34" customHeight="1">
+      <c r="A19" s="51" t="inlineStr">
+        <is>
+          <t>OEM-FR-002</t>
+        </is>
+      </c>
+      <c r="B19" s="51" t="inlineStr">
+        <is>
+          <t>SWR-003</t>
+        </is>
+      </c>
+      <c r="C19" s="51" t="n"/>
+      <c r="D19" s="51" t="n"/>
+      <c r="E19" s="51" t="n"/>
+      <c r="F19" s="51" t="n"/>
+      <c r="G19" s="51" t="n"/>
+      <c r="H19" s="49" t="n"/>
+      <c r="I19" s="49" t="inlineStr">
+        <is>
+          <t>아직 해당 단계 아님(SWE.1 완료, SWE.2 미수행) — Phase 3(2026-09-19, requirements-analyst) OEM-FR-002를 SWR-003(자동주행잠금)으로 분석, Upper Req/SW Req 열만 채움.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="34" customHeight="1">
+      <c r="A20" s="51" t="inlineStr">
+        <is>
+          <t>OEM-FR-006</t>
+        </is>
+      </c>
+      <c r="B20" s="51" t="inlineStr">
+        <is>
+          <t>SWR-018</t>
+        </is>
+      </c>
+      <c r="C20" s="51" t="n"/>
+      <c r="D20" s="51" t="n"/>
+      <c r="E20" s="51" t="n"/>
+      <c r="F20" s="51" t="n"/>
+      <c r="G20" s="51" t="n"/>
+      <c r="H20" s="49" t="n"/>
+      <c r="I20" s="49" t="inlineStr">
+        <is>
+          <t>아직 해당 단계 아님(SWE.1 완료, SWE.2 미수행) — Phase 3(2026-09-19, requirements-analyst) OEM-FR-006을 SWR-018(ISOFIX 좌우 강제잠금)로 분석, Upper Req/SW Req 열만 채움.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="34" customHeight="1">
+      <c r="A21" s="51" t="inlineStr">
+        <is>
+          <t>OEM-FR-007</t>
+        </is>
+      </c>
+      <c r="B21" s="51" t="inlineStr">
+        <is>
+          <t>SWR-020</t>
+        </is>
+      </c>
+      <c r="C21" s="51" t="n"/>
+      <c r="D21" s="51" t="n"/>
+      <c r="E21" s="51" t="n"/>
+      <c r="F21" s="51" t="n"/>
+      <c r="G21" s="51" t="n"/>
+      <c r="H21" s="49" t="n"/>
+      <c r="I21" s="49" t="inlineStr">
+        <is>
+          <t>아직 해당 단계 아님(SWE.1 완료, SWE.2 미수행) — Phase 3(2026-09-19, requirements-analyst) OEM-FR-007을 SWR-020(ignition-off 시 잠금 해제)으로 분석, Upper Req/SW Req 열만 채움.</t>
         </is>
       </c>
     </row>
@@ -1238,7 +1307,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F20"/>
+  <dimension ref="A1:F21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1724,6 +1793,38 @@
         </is>
       </c>
       <c r="F20" s="42" t="inlineStr">
+        <is>
+          <t>미승인</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="42" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
+      <c r="B21" s="42" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="C21" s="42" t="inlineStr">
+        <is>
+          <t>requirements-analyst</t>
+        </is>
+      </c>
+      <c r="D21" s="42" t="inlineStr">
+        <is>
+          <t>Phase 3 갱신 — OEM-FR-002(자동주행잠금) ↔ SWR-003, OEM-FR-006(ISOFIX 좌우 강제잠금) ↔ SWR-018, OEM-FR-007(ignition-off 해제) ↔ SWR-020 행 3건 추가(Upper Req/SW Req만 채움, ENG-SWE1-001 v0.3 갱신과 함께). Architecture 이하 열은 아직 해당 단계 아님으로 공란 유지.</t>
+        </is>
+      </c>
+      <c r="E21" s="42" t="inlineStr">
+        <is>
+          <t>초안(검토 미실시)</t>
+        </is>
+      </c>
+      <c r="F21" s="42" t="inlineStr">
         <is>
           <t>미승인</t>
         </is>

--- a/Deliverables/Engineering/Traceability/ENG-TRC-001_양방향 요구사항 추적 매트릭스.xlsx
+++ b/Deliverables/Engineering/Traceability/ENG-TRC-001_양방향 요구사항 추적 매트릭스.xlsx
@@ -1222,15 +1222,39 @@
           <t>SWR-003</t>
         </is>
       </c>
-      <c r="C19" s="51" t="n"/>
-      <c r="D19" s="51" t="n"/>
-      <c r="E19" s="51" t="n"/>
-      <c r="F19" s="51" t="n"/>
-      <c r="G19" s="51" t="n"/>
-      <c r="H19" s="49" t="n"/>
+      <c r="C19" s="51" t="inlineStr">
+        <is>
+          <t>ARC-0001, ARC-0004, ARC-0005, ARC-0009, ARC-0014 (IF-0001, IF-0005, IF-0008, IF-0009, IF-0021)</t>
+        </is>
+      </c>
+      <c r="D19" s="51" t="inlineStr">
+        <is>
+          <t>IU-0001, IU-0004(변경 없음), IU-0005(우선순위 상수 PRIORITY_AUTO_DRIVE_LOCK=6 추가, 알고리즘 코드 무변경), IU-0009, IU-0014(신규) — ENG-SWE3-001 v0.3 2장/5.12절/6.14절/7장 결정표 L</t>
+        </is>
+      </c>
+      <c r="E19" s="51" t="inlineStr">
+        <is>
+          <t>IU-0014: src/ngv/core/vehicle_speed_auto_lock_monitor.py::VehicleSpeedAutoLockMonitor(evaluate/buildLockCandidate); IU-0001: src/ngv/adapters/input_validation_adapter.py::InputValidationAdapter(validateVehicleSpeedField[신규]/normalizeCycle[갱신, 12필드]); IU-0005: src/ngv/core/command_arbiter.py::CommandArbiter(arbitrate/selectForDoor)[상수 PRIORITY_AUTO_DRIVE_LOCK=6만 추가, 알고리즘 코드 무변경 재확인]; IU-0004: src/ngv/core/output_hold_actuator.py::OutputHoldActuator(confirm)[변경 없음]; IU-0009: src/ngv/app/safety_kernel_orchestrator.py::SafetyKernelOrchestrator(evaluateCycle/evaluatePhase3Candidates[개명·확장]/assembleCandidateCommands/assemblePhase3Candidates[신규 헬퍼])[갱신]</t>
+        </is>
+      </c>
+      <c r="F19" s="51" t="inlineStr">
+        <is>
+          <t>tests/test_vehicle_speed_auto_lock_monitor.py(6, SWR-003 2.9/3.0/3.1km/h 경계값분석 포함); tests/test_input_validation_adapter.py::TestValidateVehicleSpeedField(7); tests/test_safety_kernel_orchestrator.py::TestSafetyKernelOrchestratorPhase3Wiring::testVehicleSpeedAboveThresholdLocksBothDoors(종단 검증), TestSafetyKernelOrchestratorEvaluateCycleNormalPath::testFixedCallOrderAcrossAllSubComponents(IU-0014 호출 순서 포함, 3.1절 재확인)</t>
+        </is>
+      </c>
+      <c r="G19" s="51" t="inlineStr">
+        <is>
+          <t>IT-0104~0106(IF-0021 경계값 2.9/3.0/3.1km/h), IT-0107~0108(오류주입/방어적 계약), IT-0109~0111(우선순위 4/5/6 상충), IT-0114~0116(게이트/불변조건 회귀), IT-0124~0128(IF-0001 vehicle_speed_kph 검증), IT-0130(정규화 12필드 회귀), IT-0131(전체 체인, 직전 RELEASE에서 LOCK 전환 실증), IT-0136(고정 호출 순서), IT-0137(무관 필드 무효 비차단), IT-0140(Phase1/2 인수기준 회귀) (ENG-SWE5-002). 실행 결과: ENG-SWE5-003, 전량 Pass.</t>
+        </is>
+      </c>
+      <c r="H19" s="49" t="inlineStr">
+        <is>
+          <t>ST-FUNC-0031~0035 (ENG-SWE6-001, SWR-003(a)/(b) 경계값분석 4건[2.9/3.0/3.1km/h 전이 + LOCK 유지] + 오류추측 1건[범위 오류 값 301.0]). 우선순위 교차검증: ST-FUNC-0044(crash가 자동주행잠금보다 우선), ST-FUNC-0046(ignition-off가 자동주행잠금보다 우선). 실행 결과: ENG-SWE6-002(Verification Results), 5/5 Pass(교차검증 케이스 포함 시 7/7).</t>
+        </is>
+      </c>
       <c r="I19" s="49" t="inlineStr">
         <is>
-          <t>아직 해당 단계 아님(SWE.1 완료, SWE.2 미수행) — Phase 3(2026-09-19, requirements-analyst) OEM-FR-002를 SWR-003(자동주행잠금)으로 분석, Upper Req/SW Req 열만 채움.</t>
+          <t>Code/SWE.4까지 완료(2026-09-20, coding) — SWR-003을 IU-0014로 신규 구현(2.9/3.0/3.1km/h 경계값 전수 검증, TDD Red-Green 확인). IU-0005는 상수만 추가되고 소스 변경 없음을 실측 재확인(radon cc 회귀 없음). 전체 회귀 260개 전량 Pass, 품질 게이트 5종 실측 통과. SWE.5/SWE.6은 다음 게이트. SWE.5까지 완료(2026-09-20, integration-tester) — 함수 커버리지 100%(75/75, src/ngv 전체 + testsupport), Call 커버리지 100%(coverage.py 직접실측 34/38 + 람다-튜플/다줄호출 도구 한계로 인한 런타임 증거 보완 4건, 총 38/38 아키텍처 호출관계). 전체 회귀 307개(단위137+통합140+시스템30) 전량 Pass. SWE.6까지 완료(2026-09-20, sw-system-tester) — ST-FUNC-0031~0035 5/5 Pass(ENG-SWE6-002). 2.9/3.0/3.1km/h 경계값 전수 검증, LOCK 유지(상태기반) 및 범위 오류 거절 확인. 적용 한계: 차속 3km/h 미만 재하강 시 RELEASE 복귀 여부(누적 갭 17)는 코드에 해당 로직 자체가 없어 시험 대상에서 제외. 요구사항 커버리지: SWR-003 SWE.6까지 완료 — 추적 사슬 SWE.1~SWE.6 전부 완성.</t>
         </is>
       </c>
     </row>
@@ -1245,15 +1269,39 @@
           <t>SWR-018</t>
         </is>
       </c>
-      <c r="C20" s="51" t="n"/>
-      <c r="D20" s="51" t="n"/>
-      <c r="E20" s="51" t="n"/>
-      <c r="F20" s="51" t="n"/>
-      <c r="G20" s="51" t="n"/>
-      <c r="H20" s="49" t="n"/>
+      <c r="C20" s="51" t="inlineStr">
+        <is>
+          <t>ARC-0001, ARC-0004, ARC-0005, ARC-0009, ARC-0015 (IF-0005, IF-0008, IF-0009, IF-0020, IF-0022)</t>
+        </is>
+      </c>
+      <c r="D20" s="51" t="inlineStr">
+        <is>
+          <t>IU-0001, IU-0004(변경 없음), IU-0005(우선순위 상수 PRIORITY_ISOFIX_FORCED_LOCK=5 추가, 알고리즘 코드 무변경), IU-0009, IU-0015(신규) — ENG-SWE3-001 v0.3 2장/5.13절/6.15절/7장 결정표 M</t>
+        </is>
+      </c>
+      <c r="E20" s="51" t="inlineStr">
+        <is>
+          <t>IU-0015: src/ngv/core/isofix_forced_lock_monitor.py::IsofixForcedLockMonitor(evaluate/evaluateSide); IU-0001: src/ngv/adapters/input_validation_adapter.py::InputValidationAdapter(normalizeCycle[갱신, isofixLeftField/isofixRightField — validateBooleanField 재사용]); IU-0005: src/ngv/core/command_arbiter.py::CommandArbiter(arbitrate/selectForDoor)[상수 PRIORITY_ISOFIX_FORCED_LOCK=5만 추가, 알고리즘 코드 무변경 재확인]; IU-0004: 변경 없음(행 19와 공유); IU-0009: src/ngv/app/safety_kernel_orchestrator.py::SafetyKernelOrchestrator(evaluatePhase3Candidates/assembleCandidateCommands/assemblePhase3Candidates)[갱신]</t>
+        </is>
+      </c>
+      <c r="F20" s="51" t="inlineStr">
+        <is>
+          <t>tests/test_isofix_forced_lock_monitor.py(7, SWR-018(b) 좌우 4조합 FF/FT/TF/TT 전수 포함); tests/test_safety_kernel_orchestrator.py::TestSafetyKernelOrchestratorPhase3Wiring::testIsofixLeftLocksOnlyLeftDoor(종단 검증)</t>
+        </is>
+      </c>
+      <c r="G20" s="51" t="inlineStr">
+        <is>
+          <t>IT-0098~0101(IF-0022 좌우 4조합 FF/FT/TF/TT), IT-0102~0103(오류주입/방어적 계약), IT-0109/0111/0113(우선순위 5 상충), IT-0114~0116(게이트/불변조건 회귀), IT-0129(IF-0020 isofix_left/right 검증), IT-0130(정규화 12필드 회귀), IT-0132(전체 체인, 좌우 독립 실증), IT-0134(전체 체인 우선순위 상충), IT-0136(고정 호출 순서), IT-0138(무관 필드 무효 비차단) (ENG-SWE5-002). 실행 결과: ENG-SWE5-003, 전량 Pass.</t>
+        </is>
+      </c>
+      <c r="H20" s="49" t="inlineStr">
+        <is>
+          <t>ST-FUNC-0036~0040 (ENG-SWE6-001, SWR-018 전 조건 조합 4건[좌/우 isofix FF/FT/TF/TT] + 오류추측 1건[좌측 형식오류+우측 독립]). 우선순위 교차검증: ST-FUNC-0045(fire가 ISOFIX보다 우선), ST-FUNC-0046(ignition-off가 ISOFIX보다 우선). 실행 결과: ENG-SWE6-002(Verification Results), 5/5 Pass(교차검증 케이스 포함 시 7/7).</t>
+        </is>
+      </c>
       <c r="I20" s="49" t="inlineStr">
         <is>
-          <t>아직 해당 단계 아님(SWE.1 완료, SWE.2 미수행) — Phase 3(2026-09-19, requirements-analyst) OEM-FR-006을 SWR-018(ISOFIX 좌우 강제잠금)로 분석, Upper Req/SW Req 열만 채움.</t>
+          <t>Code/SWE.4까지 완료(2026-09-20, coding) — SWR-018을 IU-0015로 신규 구현(좌우 독립, evaluateSide 패턴으로 IU-0011과 동일 구조 — 4조합 FF/FT/TF/TT 전수 검증). 해제요청 억제 여부는 갭 14로 유지(별도 메커니즘 미구현, 설계 결정 그대로 구현). 전체 회귀 260개 전량 Pass, 품질 게이트 5종 실측 통과. SWE.5/SWE.6은 다음 게이트. SWE.5까지 완료(2026-09-20, integration-tester) — 함수 커버리지 100%(75/75, src/ngv 전체 + testsupport), Call 커버리지 100%(coverage.py 직접실측 34/38 + 람다-튜플/다줄호출 도구 한계로 인한 런타임 증거 보완 4건, 총 38/38 아키텍처 호출관계). 전체 회귀 307개(단위137+통합140+시스템30) 전량 Pass. SWE.6까지 완료(2026-09-20, sw-system-tester) — ST-FUNC-0036~0040 5/5 Pass(ENG-SWE6-002). 좌우 4조합 전수 검증(독립성 포함) 및 형식 오류 거절 확인. 적용 한계: isofix TRUE인 동안 해제요청 명시적 억제 여부(누적 갭 14)는 억제 메커니즘 자체가 설계/코드에 없어 시험 대상에서 제외. 요구사항 커버리지: SWR-018 SWE.6까지 완료 — 추적 사슬 SWE.1~SWE.6 전부 완성.</t>
         </is>
       </c>
     </row>
@@ -1268,15 +1316,39 @@
           <t>SWR-020</t>
         </is>
       </c>
-      <c r="C21" s="51" t="n"/>
-      <c r="D21" s="51" t="n"/>
-      <c r="E21" s="51" t="n"/>
-      <c r="F21" s="51" t="n"/>
-      <c r="G21" s="51" t="n"/>
-      <c r="H21" s="49" t="n"/>
+      <c r="C21" s="51" t="inlineStr">
+        <is>
+          <t>ARC-0001, ARC-0003, ARC-0004, ARC-0005, ARC-0007, ARC-0009, ARC-0016 (IF-0002, IF-0004, IF-0005, IF-0007, IF-0008, IF-0009, IF-0011, IF-0023)</t>
+        </is>
+      </c>
+      <c r="D21" s="51" t="inlineStr">
+        <is>
+          <t>IU-0001, IU-0003(OFF 판정 신규, 갱신), IU-0004(변경 없음), IU-0005(우선순위 상수 PRIORITY_IGNITION_OFF_RELEASE=4 추가, 알고리즘 코드 무변경), IU-0007(변경 없음), IU-0009, IU-0016(신규) — ENG-SWE3-001 v0.3 2장/5.11절/5.14절/6.13절/6.16절/7장 결정표 K/N/8.7~8.9절</t>
+        </is>
+      </c>
+      <c r="E21" s="51" t="inlineStr">
+        <is>
+          <t>IU-0016: src/ngv/core/ignition_off_release_monitor.py::IgnitionOffReleaseMonitor(evaluate/buildReleaseCandidate); IU-0003: src/ngv/core/state_manager.py::StateManager(evaluate/decideState/decideWarningReasonCode/reset)[OFF 판정 신규, ignitionOnField 파라미터 추가 — Phase3에서 최초 갱신]; IU-0001/IU-0005/IU-0009: 상동(행 19와 동일 갱신분 공유); IU-0004/IU-0007: 변경 없음</t>
+        </is>
+      </c>
+      <c r="F21" s="51" t="inlineStr">
+        <is>
+          <t>tests/test_ignition_off_release_monitor.py(5); tests/test_state_manager.py::TestStateManagerOffState(6, ignitionOnField.valid=False 시 OFF 미판정 회귀 테스트 testIgnitionInvalidFieldFallsBackToNormalNotOff/testIgnitionInvalidFieldFallsBackToDegradedNotOffWhenStale 포함) + TestStateManagerFourStateCombinations(1, FAULT/OFF/DEGRADED/NORMAL 8개 조합 전수 subTest); tests/test_safety_kernel_orchestrator.py::TestSafetyKernelOrchestratorPhase3Wiring::testIgnitionOffReleasesBothDoors(종단 검증)</t>
+        </is>
+      </c>
+      <c r="G21" s="51" t="inlineStr">
+        <is>
+          <t>IT-0094~0095(IF-0023 valid True/False), IT-0096~0097(오류주입/방어적 계약), IT-0109/0110/0112(우선순위 4 상충, IT-0112는 누적 갭16 현재 동작 문서화), IT-0114~0116(게이트/불변조건 회귀), IT-0117~0123(IF-0007 OFF 상태 판정 전 조합, IT-0121은 ignitionOnField invalid 시 OFF 미판정 회귀 확인), IT-0133(전체 체인, OFF 상태+RELEASE 실증), IT-0134~0135(전체 체인 우선순위 상충, IT-0135는 누적 갭16 현재 동작 문서화), IT-0136(고정 호출 순서), IT-0139(전체 체인 ignitionOnField invalid 시 OFF 미판정+INPUT_INVALID 회귀), IT-0140(Phase1/2 인수기준 회귀) (ENG-SWE5-002). 실행 결과: ENG-SWE5-003, 전량 Pass.</t>
+        </is>
+      </c>
+      <c r="H21" s="49" t="inlineStr">
+        <is>
+          <t>ST-FUNC-0041~0043 (ENG-SWE6-001, SWR-020(a) 요구사항 기반 시험 1건[이벤트기반 전이+RELEASE/OFF/이유코드] + SWR-020(b) 상태전이 테스트 1건[RELEASE/OFF 유지] + 오류추측 1건[ignitionOnField invalid 시 OFF 미판정 회귀]). 우선순위 교차검증: ST-FUNC-0046(ignition-off가 ISOFIX/자동주행잠금보다 우선), ST-FUNC-0047(접근위험(ASIL B) vs ignition-off(QM) 현재 동작 재확인, 갭16 단정 금지). 실행 결과: ENG-SWE6-002(Verification Results), 3/3 Pass(교차검증 케이스 포함 시 5/5).</t>
+        </is>
+      </c>
       <c r="I21" s="49" t="inlineStr">
         <is>
-          <t>아직 해당 단계 아님(SWE.1 완료, SWE.2 미수행) — Phase 3(2026-09-19, requirements-analyst) OEM-FR-007을 SWR-020(ignition-off 시 잠금 해제)으로 분석, Upper Req/SW Req 열만 채움.</t>
+          <t>Code/SWE.4까지 완료(2026-09-20, coding) — SWR-020을 IU-0016(후보 생성)+IU-0003(OFF 상태 판정, FAULT&gt;OFF&gt;DEGRADED&gt;NORMAL) 조합으로 신규/갱신 구현. ignitionOnField.valid=False 시 OFF 미판정/후보 미생성 원칙을 IU-0003/IU-0016 양쪽에서 동일하게 구현하고 회귀 테스트로 고정(8.8절). 전체 회귀 260개 전량 Pass, 품질 게이트 5종 실측 통과. SWE.5/SWE.6은 다음 게이트. SWE.5까지 완료(2026-09-20, integration-tester) — 함수 커버리지 100%(75/75, src/ngv 전체 + testsupport), Call 커버리지 100%(coverage.py 직접실측 34/38 + 람다-튜플/다줄호출 도구 한계로 인한 런타임 증거 보완 4건, 총 38/38 아키텍처 호출관계). 전체 회귀 307개(단위137+통합140+시스템30) 전량 Pass. SWE.6까지 완료(2026-09-20, sw-system-tester) — ST-FUNC-0041~0043 3/3 Pass(ENG-SWE6-002). ignition_on TRUE→FALSE 전이 시 RELEASE/OFF/이유코드(stateResult.warningReasonCode) 전부 직접 관측 가능함을 확인(Phase2 이유코드와 달리 구조적 관측 한계 없음). ignitionOnField 형식 오류 시 OFF 미판정(ENG-SWE3-001 8.8절 SW 설계 재량)을 시스템 경계에서 회귀 고정. 적용 한계: OFF와 DEGRADED/FAULT 동시성(누적 갭 15는 아키텍처 단계에서 판정 순서로 해소됨, 다만 그 세부 시나리오)과 접근위험(ASIL B) vs ignition-off(QM) 최종 우선순위(누적 갭 16)는 ST-FUNC-0047이 현재 동작만 재확인했을 뿐 OEM-A 확인 없이 최종 확정으로 단정하지 않는다. 요구사항 커버리지: SWR-020 SWE.6까지 완료 — 추적 사슬 SWE.1~SWE.6 전부 완성.</t>
         </is>
       </c>
     </row>
@@ -1307,7 +1379,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:F26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1825,6 +1897,166 @@
         </is>
       </c>
       <c r="F21" s="42" t="inlineStr">
+        <is>
+          <t>미승인</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="42" t="inlineStr">
+        <is>
+          <t>1.3</t>
+        </is>
+      </c>
+      <c r="B22" s="42" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="C22" s="42" t="inlineStr">
+        <is>
+          <t>architecture-designer</t>
+        </is>
+      </c>
+      <c r="D22" s="42" t="inlineStr">
+        <is>
+          <t>Phase 3 아키텍처 설계 — ENG-SWE2-001 v0.3/ENG-SWE2-002 갱신(ARC-0014~0016 신규, ARC-0001/0003/0005/0009 확장, IF-0020~IF-0023 신규). Architecture 열(ARC-NNNN/IF-NNNN) 및 Coverage 열 갱신 — SWR-003/018/020 대상 3개 행(OEM-FR-002/FR-006/FR-007). 우선순위 체인 확장(4=ignition-off해제, 5=ISOFIX강제잠금, 6=자동주행잠금), SystemState에 OFF 추가(FAULT&gt;OFF&gt;DEGRADED&gt;NORMAL).</t>
+        </is>
+      </c>
+      <c r="E22" s="42" t="inlineStr">
+        <is>
+          <t>초안(검토 미실시)</t>
+        </is>
+      </c>
+      <c r="F22" s="42" t="inlineStr">
+        <is>
+          <t>미승인</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>1.4</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>detailed-designer</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>SWR-003/018/020(OEM-FR-002/006/007) 3개 행의 Detailed Design/Coverage 열을 채움 — IU-0014(신규, 자동주행잠금)/IU-0015(신규, ISOFIX강제잠금)/IU-0016(신규, ignition-off해제 후보생성) 및 IU-0001/0003/0005/0009 갱신분 반영(ENG-SWE3-001 v0.3 근거).</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>검토 미실시</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>미승인</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>coding</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Phase 3 구현(TDD) — src/ngv/core 이하 IU-0014(vehicle_speed_auto_lock_monitor.py)/IU-0015(isofix_forced_lock_monitor.py)/IU-0016(ignition_off_release_monitor.py) 신규 구현, IU-0001(validateVehicleSpeedField 신규+normalizeCycle 12필드 확장)/IU-0003(evaluate에 ignitionOnField 파라미터 추가, decideState/decideWarningReasonCode 헬퍼 분리로 OFF 판정 신규 구현)/IU-0009(evaluatePhase2Candidates를 evaluatePhase3Candidates로 개명·확장, assembleCandidateCommands에 Phase3 3필드 추가+assemblePhase2/3Candidates로 순환복잡도 분리) 갱신. IU-0005(command_arbiter.py)는 설계대로 소스 변경 없음(상수 3개만 constants.py에 추가) 실측 재확인. testsupport/orchestrator_factory.py에 IU-0014~0016 기본값 추가. 기존 tests/test_state_manager.py(전 호출부에 ignitionOnField 인자 추가)/tests_integration/test_it_step2_state_manager.py/test_it_step6_orchestrator_integration.py/test_it_step14_orchestrator_phase2_integration.py(오케스트레이터 생성자 확장에 따른 기계적 동기화만, 신규 IT- 케이스 설계 없음). 단위테스트 137개(Phase2까지 98개+Phase3 신규 39개), 전체 회귀(단위137+통합93+시스템30=260개) 전량 Pass. 품질 게이트 5종(radon cc 최대 복잡도 9[assembleCandidateCommands 분리 전 11 위반을 분리로 해소]; 함수별 순수코드라인 전부 ≤50; pylint duplicate-code 위반 0; pylint invalid-name 위반 0; radon raw 주석비율 29~49%) 신규/변경 파일 전부 실측 통과. Code/SWE.4/Coverage 열 갱신(SWR-003/018/020 대상 3개 행). SWE.5/SWE.6(신규 IT-/ST- 케이스)는 다음 게이트.</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>검토 미실시</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>미승인</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>1.6</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>integration-tester</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Phase 3 SWE.5 — SWR-003/018/020(OEM-FR-002/FR-006/FR-007) 3개 행의 SWE.5(G)/Coverage(I) 열을 갱신(IT-0094~IT-0140 매핑, 함수/Call 커버리지 100% 실측치 반영).</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>초안(검토 미실시)</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>미승인</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>1.7</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>sw-system-tester</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Phase 3 SWE.6(마지막 게이트) - SWR-003/018/020(OEM-FR-002/FR-006/FR-007) 3개 행의 SWE.6(H)/Coverage(I) 열을 갱신(ST-FUNC-0031~0047 매핑, 17/17 Pass, 우선순위 결정표 교차검증 포함). 이 갱신으로 SWR-003/018/020 3개 요구사항의 추적 사슬이 SWE.1부터 SWE.6까지 전부 완성됨. Phase 3 전체 게이트(SWE.1~SWE.6) 완료.</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>초안(검토 미실시)</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
         <is>
           <t>미승인</t>
         </is>

--- a/Deliverables/Engineering/Traceability/ENG-TRC-001_양방향 요구사항 추적 매트릭스.xlsx
+++ b/Deliverables/Engineering/Traceability/ENG-TRC-001_양방향 요구사항 추적 매트릭스.xlsx
@@ -619,7 +619,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I18"/>
+  <dimension ref="A1:I21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -704,7 +704,7 @@
       </c>
       <c r="F4" s="9" t="inlineStr">
         <is>
-          <t>v0.2 (Draft) — Phase 2(안전 긴급 대응) 갱신, Phase 1 내용 유지</t>
+          <t>v0.3 (Draft) — Phase 3(자동주행잠금/ISOFIX강제잠금/ignition-off해제) 갱신, Phase 1/2 내용 유지</t>
         </is>
       </c>
       <c r="G4" s="9" t="str"/>
@@ -1208,6 +1208,147 @@
       <c r="I18" s="49" t="inlineStr">
         <is>
           <t>SWE.6까지 완료(2026-09-19, sw-system-tester) — ST-FUNC-0027~0030 4/4 Pass(ENG-SWE6-002). 3개 입력 각각 단독 트리거 시 RELEASE 전환 및 복수 입력 동시발생 시 RELEASE 유지 확인. 적용 한계: 이유코드(입력별) 기록은 CycleResult 미노출(ledger 갭 10)로 시스템 경계에서 직접 관측 불가(하위 IT-0062~0068에서 이미 검증됨). 요구사항 커버리지: SWR-017 SWE.6까지 완료.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="34" customHeight="1">
+      <c r="A19" s="51" t="inlineStr">
+        <is>
+          <t>OEM-FR-002</t>
+        </is>
+      </c>
+      <c r="B19" s="51" t="inlineStr">
+        <is>
+          <t>SWR-003</t>
+        </is>
+      </c>
+      <c r="C19" s="51" t="inlineStr">
+        <is>
+          <t>ARC-0001, ARC-0004, ARC-0005, ARC-0009, ARC-0014 (IF-0001, IF-0005, IF-0008, IF-0009, IF-0021)</t>
+        </is>
+      </c>
+      <c r="D19" s="51" t="inlineStr">
+        <is>
+          <t>IU-0001, IU-0004(변경 없음), IU-0005(우선순위 상수 PRIORITY_AUTO_DRIVE_LOCK=6 추가, 알고리즘 코드 무변경), IU-0009, IU-0014(신규) — ENG-SWE3-001 v0.3 2장/5.12절/6.14절/7장 결정표 L</t>
+        </is>
+      </c>
+      <c r="E19" s="51" t="inlineStr">
+        <is>
+          <t>IU-0014: src/ngv/core/vehicle_speed_auto_lock_monitor.py::VehicleSpeedAutoLockMonitor(evaluate/buildLockCandidate); IU-0001: src/ngv/adapters/input_validation_adapter.py::InputValidationAdapter(validateVehicleSpeedField[신규]/normalizeCycle[갱신, 12필드]); IU-0005: src/ngv/core/command_arbiter.py::CommandArbiter(arbitrate/selectForDoor)[상수 PRIORITY_AUTO_DRIVE_LOCK=6만 추가, 알고리즘 코드 무변경 재확인]; IU-0004: src/ngv/core/output_hold_actuator.py::OutputHoldActuator(confirm)[변경 없음]; IU-0009: src/ngv/app/safety_kernel_orchestrator.py::SafetyKernelOrchestrator(evaluateCycle/evaluatePhase3Candidates[개명·확장]/assembleCandidateCommands/assemblePhase3Candidates[신규 헬퍼])[갱신]</t>
+        </is>
+      </c>
+      <c r="F19" s="51" t="inlineStr">
+        <is>
+          <t>tests/test_vehicle_speed_auto_lock_monitor.py(6, SWR-003 2.9/3.0/3.1km/h 경계값분석 포함); tests/test_input_validation_adapter.py::TestValidateVehicleSpeedField(7); tests/test_safety_kernel_orchestrator.py::TestSafetyKernelOrchestratorPhase3Wiring::testVehicleSpeedAboveThresholdLocksBothDoors(종단 검증), TestSafetyKernelOrchestratorEvaluateCycleNormalPath::testFixedCallOrderAcrossAllSubComponents(IU-0014 호출 순서 포함, 3.1절 재확인)</t>
+        </is>
+      </c>
+      <c r="G19" s="51" t="inlineStr">
+        <is>
+          <t>IT-0104~0106(IF-0021 경계값 2.9/3.0/3.1km/h), IT-0107~0108(오류주입/방어적 계약), IT-0109~0111(우선순위 4/5/6 상충), IT-0114~0116(게이트/불변조건 회귀), IT-0124~0128(IF-0001 vehicle_speed_kph 검증), IT-0130(정규화 12필드 회귀), IT-0131(전체 체인, 직전 RELEASE에서 LOCK 전환 실증), IT-0136(고정 호출 순서), IT-0137(무관 필드 무효 비차단), IT-0140(Phase1/2 인수기준 회귀) (ENG-SWE5-002). 실행 결과: ENG-SWE5-003, 전량 Pass.</t>
+        </is>
+      </c>
+      <c r="H19" s="49" t="inlineStr">
+        <is>
+          <t>ST-FUNC-0031~0035 (ENG-SWE6-001, SWR-003(a)/(b) 경계값분석 4건[2.9/3.0/3.1km/h 전이 + LOCK 유지] + 오류추측 1건[범위 오류 값 301.0]). 우선순위 교차검증: ST-FUNC-0044(crash가 자동주행잠금보다 우선), ST-FUNC-0046(ignition-off가 자동주행잠금보다 우선). 실행 결과: ENG-SWE6-002(Verification Results), 5/5 Pass(교차검증 케이스 포함 시 7/7).</t>
+        </is>
+      </c>
+      <c r="I19" s="49" t="inlineStr">
+        <is>
+          <t>Code/SWE.4까지 완료(2026-09-20, coding) — SWR-003을 IU-0014로 신규 구현(2.9/3.0/3.1km/h 경계값 전수 검증, TDD Red-Green 확인). IU-0005는 상수만 추가되고 소스 변경 없음을 실측 재확인(radon cc 회귀 없음). 전체 회귀 260개 전량 Pass, 품질 게이트 5종 실측 통과. SWE.5/SWE.6은 다음 게이트. SWE.5까지 완료(2026-09-20, integration-tester) — 함수 커버리지 100%(75/75, src/ngv 전체 + testsupport), Call 커버리지 100%(coverage.py 직접실측 34/38 + 람다-튜플/다줄호출 도구 한계로 인한 런타임 증거 보완 4건, 총 38/38 아키텍처 호출관계). 전체 회귀 307개(단위137+통합140+시스템30) 전량 Pass. SWE.6까지 완료(2026-09-20, sw-system-tester) — ST-FUNC-0031~0035 5/5 Pass(ENG-SWE6-002). 2.9/3.0/3.1km/h 경계값 전수 검증, LOCK 유지(상태기반) 및 범위 오류 거절 확인. 적용 한계: 차속 3km/h 미만 재하강 시 RELEASE 복귀 여부(누적 갭 17)는 코드에 해당 로직 자체가 없어 시험 대상에서 제외. 요구사항 커버리지: SWR-003 SWE.6까지 완료 — 추적 사슬 SWE.1~SWE.6 전부 완성.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="34" customHeight="1">
+      <c r="A20" s="51" t="inlineStr">
+        <is>
+          <t>OEM-FR-006</t>
+        </is>
+      </c>
+      <c r="B20" s="51" t="inlineStr">
+        <is>
+          <t>SWR-018</t>
+        </is>
+      </c>
+      <c r="C20" s="51" t="inlineStr">
+        <is>
+          <t>ARC-0001, ARC-0004, ARC-0005, ARC-0009, ARC-0015 (IF-0005, IF-0008, IF-0009, IF-0020, IF-0022)</t>
+        </is>
+      </c>
+      <c r="D20" s="51" t="inlineStr">
+        <is>
+          <t>IU-0001, IU-0004(변경 없음), IU-0005(우선순위 상수 PRIORITY_ISOFIX_FORCED_LOCK=5 추가, 알고리즘 코드 무변경), IU-0009, IU-0015(신규) — ENG-SWE3-001 v0.3 2장/5.13절/6.15절/7장 결정표 M</t>
+        </is>
+      </c>
+      <c r="E20" s="51" t="inlineStr">
+        <is>
+          <t>IU-0015: src/ngv/core/isofix_forced_lock_monitor.py::IsofixForcedLockMonitor(evaluate/evaluateSide); IU-0001: src/ngv/adapters/input_validation_adapter.py::InputValidationAdapter(normalizeCycle[갱신, isofixLeftField/isofixRightField — validateBooleanField 재사용]); IU-0005: src/ngv/core/command_arbiter.py::CommandArbiter(arbitrate/selectForDoor)[상수 PRIORITY_ISOFIX_FORCED_LOCK=5만 추가, 알고리즘 코드 무변경 재확인]; IU-0004: 변경 없음(행 19와 공유); IU-0009: src/ngv/app/safety_kernel_orchestrator.py::SafetyKernelOrchestrator(evaluatePhase3Candidates/assembleCandidateCommands/assemblePhase3Candidates)[갱신]</t>
+        </is>
+      </c>
+      <c r="F20" s="51" t="inlineStr">
+        <is>
+          <t>tests/test_isofix_forced_lock_monitor.py(7, SWR-018(b) 좌우 4조합 FF/FT/TF/TT 전수 포함); tests/test_safety_kernel_orchestrator.py::TestSafetyKernelOrchestratorPhase3Wiring::testIsofixLeftLocksOnlyLeftDoor(종단 검증)</t>
+        </is>
+      </c>
+      <c r="G20" s="51" t="inlineStr">
+        <is>
+          <t>IT-0098~0101(IF-0022 좌우 4조합 FF/FT/TF/TT), IT-0102~0103(오류주입/방어적 계약), IT-0109/0111/0113(우선순위 5 상충), IT-0114~0116(게이트/불변조건 회귀), IT-0129(IF-0020 isofix_left/right 검증), IT-0130(정규화 12필드 회귀), IT-0132(전체 체인, 좌우 독립 실증), IT-0134(전체 체인 우선순위 상충), IT-0136(고정 호출 순서), IT-0138(무관 필드 무효 비차단) (ENG-SWE5-002). 실행 결과: ENG-SWE5-003, 전량 Pass.</t>
+        </is>
+      </c>
+      <c r="H20" s="49" t="inlineStr">
+        <is>
+          <t>ST-FUNC-0036~0040 (ENG-SWE6-001, SWR-018 전 조건 조합 4건[좌/우 isofix FF/FT/TF/TT] + 오류추측 1건[좌측 형식오류+우측 독립]). 우선순위 교차검증: ST-FUNC-0045(fire가 ISOFIX보다 우선), ST-FUNC-0046(ignition-off가 ISOFIX보다 우선). 실행 결과: ENG-SWE6-002(Verification Results), 5/5 Pass(교차검증 케이스 포함 시 7/7).</t>
+        </is>
+      </c>
+      <c r="I20" s="49" t="inlineStr">
+        <is>
+          <t>Code/SWE.4까지 완료(2026-09-20, coding) — SWR-018을 IU-0015로 신규 구현(좌우 독립, evaluateSide 패턴으로 IU-0011과 동일 구조 — 4조합 FF/FT/TF/TT 전수 검증). 해제요청 억제 여부는 갭 14로 유지(별도 메커니즘 미구현, 설계 결정 그대로 구현). 전체 회귀 260개 전량 Pass, 품질 게이트 5종 실측 통과. SWE.5/SWE.6은 다음 게이트. SWE.5까지 완료(2026-09-20, integration-tester) — 함수 커버리지 100%(75/75, src/ngv 전체 + testsupport), Call 커버리지 100%(coverage.py 직접실측 34/38 + 람다-튜플/다줄호출 도구 한계로 인한 런타임 증거 보완 4건, 총 38/38 아키텍처 호출관계). 전체 회귀 307개(단위137+통합140+시스템30) 전량 Pass. SWE.6까지 완료(2026-09-20, sw-system-tester) — ST-FUNC-0036~0040 5/5 Pass(ENG-SWE6-002). 좌우 4조합 전수 검증(독립성 포함) 및 형식 오류 거절 확인. 적용 한계: isofix TRUE인 동안 해제요청 명시적 억제 여부(누적 갭 14)는 억제 메커니즘 자체가 설계/코드에 없어 시험 대상에서 제외. 요구사항 커버리지: SWR-018 SWE.6까지 완료 — 추적 사슬 SWE.1~SWE.6 전부 완성.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="34" customHeight="1">
+      <c r="A21" s="51" t="inlineStr">
+        <is>
+          <t>OEM-FR-007</t>
+        </is>
+      </c>
+      <c r="B21" s="51" t="inlineStr">
+        <is>
+          <t>SWR-020</t>
+        </is>
+      </c>
+      <c r="C21" s="51" t="inlineStr">
+        <is>
+          <t>ARC-0001, ARC-0003, ARC-0004, ARC-0005, ARC-0007, ARC-0009, ARC-0016 (IF-0002, IF-0004, IF-0005, IF-0007, IF-0008, IF-0009, IF-0011, IF-0023)</t>
+        </is>
+      </c>
+      <c r="D21" s="51" t="inlineStr">
+        <is>
+          <t>IU-0001, IU-0003(OFF 판정 신규, 갱신), IU-0004(변경 없음), IU-0005(우선순위 상수 PRIORITY_IGNITION_OFF_RELEASE=4 추가, 알고리즘 코드 무변경), IU-0007(변경 없음), IU-0009, IU-0016(신규) — ENG-SWE3-001 v0.3 2장/5.11절/5.14절/6.13절/6.16절/7장 결정표 K/N/8.7~8.9절</t>
+        </is>
+      </c>
+      <c r="E21" s="51" t="inlineStr">
+        <is>
+          <t>IU-0016: src/ngv/core/ignition_off_release_monitor.py::IgnitionOffReleaseMonitor(evaluate/buildReleaseCandidate); IU-0003: src/ngv/core/state_manager.py::StateManager(evaluate/decideState/decideWarningReasonCode/reset)[OFF 판정 신규, ignitionOnField 파라미터 추가 — Phase3에서 최초 갱신]; IU-0001/IU-0005/IU-0009: 상동(행 19와 동일 갱신분 공유); IU-0004/IU-0007: 변경 없음</t>
+        </is>
+      </c>
+      <c r="F21" s="51" t="inlineStr">
+        <is>
+          <t>tests/test_ignition_off_release_monitor.py(5); tests/test_state_manager.py::TestStateManagerOffState(6, ignitionOnField.valid=False 시 OFF 미판정 회귀 테스트 testIgnitionInvalidFieldFallsBackToNormalNotOff/testIgnitionInvalidFieldFallsBackToDegradedNotOffWhenStale 포함) + TestStateManagerFourStateCombinations(1, FAULT/OFF/DEGRADED/NORMAL 8개 조합 전수 subTest); tests/test_safety_kernel_orchestrator.py::TestSafetyKernelOrchestratorPhase3Wiring::testIgnitionOffReleasesBothDoors(종단 검증)</t>
+        </is>
+      </c>
+      <c r="G21" s="51" t="inlineStr">
+        <is>
+          <t>IT-0094~0095(IF-0023 valid True/False), IT-0096~0097(오류주입/방어적 계약), IT-0109/0110/0112(우선순위 4 상충, IT-0112는 누적 갭16 현재 동작 문서화), IT-0114~0116(게이트/불변조건 회귀), IT-0117~0123(IF-0007 OFF 상태 판정 전 조합, IT-0121은 ignitionOnField invalid 시 OFF 미판정 회귀 확인), IT-0133(전체 체인, OFF 상태+RELEASE 실증), IT-0134~0135(전체 체인 우선순위 상충, IT-0135는 누적 갭16 현재 동작 문서화), IT-0136(고정 호출 순서), IT-0139(전체 체인 ignitionOnField invalid 시 OFF 미판정+INPUT_INVALID 회귀), IT-0140(Phase1/2 인수기준 회귀) (ENG-SWE5-002). 실행 결과: ENG-SWE5-003, 전량 Pass.</t>
+        </is>
+      </c>
+      <c r="H21" s="49" t="inlineStr">
+        <is>
+          <t>ST-FUNC-0041~0043 (ENG-SWE6-001, SWR-020(a) 요구사항 기반 시험 1건[이벤트기반 전이+RELEASE/OFF/이유코드] + SWR-020(b) 상태전이 테스트 1건[RELEASE/OFF 유지] + 오류추측 1건[ignitionOnField invalid 시 OFF 미판정 회귀]). 우선순위 교차검증: ST-FUNC-0046(ignition-off가 ISOFIX/자동주행잠금보다 우선), ST-FUNC-0047(접근위험(ASIL B) vs ignition-off(QM) 현재 동작 재확인, 갭16 단정 금지). 실행 결과: ENG-SWE6-002(Verification Results), 3/3 Pass(교차검증 케이스 포함 시 5/5).</t>
+        </is>
+      </c>
+      <c r="I21" s="49" t="inlineStr">
+        <is>
+          <t>Code/SWE.4까지 완료(2026-09-20, coding) — SWR-020을 IU-0016(후보 생성)+IU-0003(OFF 상태 판정, FAULT&gt;OFF&gt;DEGRADED&gt;NORMAL) 조합으로 신규/갱신 구현. ignitionOnField.valid=False 시 OFF 미판정/후보 미생성 원칙을 IU-0003/IU-0016 양쪽에서 동일하게 구현하고 회귀 테스트로 고정(8.8절). 전체 회귀 260개 전량 Pass, 품질 게이트 5종 실측 통과. SWE.5/SWE.6은 다음 게이트. SWE.5까지 완료(2026-09-20, integration-tester) — 함수 커버리지 100%(75/75, src/ngv 전체 + testsupport), Call 커버리지 100%(coverage.py 직접실측 34/38 + 람다-튜플/다줄호출 도구 한계로 인한 런타임 증거 보완 4건, 총 38/38 아키텍처 호출관계). 전체 회귀 307개(단위137+통합140+시스템30) 전량 Pass. SWE.6까지 완료(2026-09-20, sw-system-tester) — ST-FUNC-0041~0043 3/3 Pass(ENG-SWE6-002). ignition_on TRUE→FALSE 전이 시 RELEASE/OFF/이유코드(stateResult.warningReasonCode) 전부 직접 관측 가능함을 확인(Phase2 이유코드와 달리 구조적 관측 한계 없음). ignitionOnField 형식 오류 시 OFF 미판정(ENG-SWE3-001 8.8절 SW 설계 재량)을 시스템 경계에서 회귀 고정. 적용 한계: OFF와 DEGRADED/FAULT 동시성(누적 갭 15는 아키텍처 단계에서 판정 순서로 해소됨, 다만 그 세부 시나리오)과 접근위험(ASIL B) vs ignition-off(QM) 최종 우선순위(누적 갭 16)는 ST-FUNC-0047이 현재 동작만 재확인했을 뿐 OEM-A 확인 없이 최종 확정으로 단정하지 않는다. 요구사항 커버리지: SWR-020 SWE.6까지 완료 — 추적 사슬 SWE.1~SWE.6 전부 완성.</t>
         </is>
       </c>
     </row>
@@ -1238,7 +1379,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F20"/>
+  <dimension ref="A1:F26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1724,6 +1865,198 @@
         </is>
       </c>
       <c r="F20" s="42" t="inlineStr">
+        <is>
+          <t>미승인</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="42" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
+      <c r="B21" s="42" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="C21" s="42" t="inlineStr">
+        <is>
+          <t>requirements-analyst</t>
+        </is>
+      </c>
+      <c r="D21" s="42" t="inlineStr">
+        <is>
+          <t>Phase 3 갱신 — OEM-FR-002(자동주행잠금) ↔ SWR-003, OEM-FR-006(ISOFIX 좌우 강제잠금) ↔ SWR-018, OEM-FR-007(ignition-off 해제) ↔ SWR-020 행 3건 추가(Upper Req/SW Req만 채움, ENG-SWE1-001 v0.3 갱신과 함께). Architecture 이하 열은 아직 해당 단계 아님으로 공란 유지.</t>
+        </is>
+      </c>
+      <c r="E21" s="42" t="inlineStr">
+        <is>
+          <t>초안(검토 미실시)</t>
+        </is>
+      </c>
+      <c r="F21" s="42" t="inlineStr">
+        <is>
+          <t>미승인</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="42" t="inlineStr">
+        <is>
+          <t>1.3</t>
+        </is>
+      </c>
+      <c r="B22" s="42" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="C22" s="42" t="inlineStr">
+        <is>
+          <t>architecture-designer</t>
+        </is>
+      </c>
+      <c r="D22" s="42" t="inlineStr">
+        <is>
+          <t>Phase 3 아키텍처 설계 — ENG-SWE2-001 v0.3/ENG-SWE2-002 갱신(ARC-0014~0016 신규, ARC-0001/0003/0005/0009 확장, IF-0020~IF-0023 신규). Architecture 열(ARC-NNNN/IF-NNNN) 및 Coverage 열 갱신 — SWR-003/018/020 대상 3개 행(OEM-FR-002/FR-006/FR-007). 우선순위 체인 확장(4=ignition-off해제, 5=ISOFIX강제잠금, 6=자동주행잠금), SystemState에 OFF 추가(FAULT&gt;OFF&gt;DEGRADED&gt;NORMAL).</t>
+        </is>
+      </c>
+      <c r="E22" s="42" t="inlineStr">
+        <is>
+          <t>초안(검토 미실시)</t>
+        </is>
+      </c>
+      <c r="F22" s="42" t="inlineStr">
+        <is>
+          <t>미승인</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>1.4</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>detailed-designer</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>SWR-003/018/020(OEM-FR-002/006/007) 3개 행의 Detailed Design/Coverage 열을 채움 — IU-0014(신규, 자동주행잠금)/IU-0015(신규, ISOFIX강제잠금)/IU-0016(신규, ignition-off해제 후보생성) 및 IU-0001/0003/0005/0009 갱신분 반영(ENG-SWE3-001 v0.3 근거).</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>검토 미실시</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>미승인</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>coding</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Phase 3 구현(TDD) — src/ngv/core 이하 IU-0014(vehicle_speed_auto_lock_monitor.py)/IU-0015(isofix_forced_lock_monitor.py)/IU-0016(ignition_off_release_monitor.py) 신규 구현, IU-0001(validateVehicleSpeedField 신규+normalizeCycle 12필드 확장)/IU-0003(evaluate에 ignitionOnField 파라미터 추가, decideState/decideWarningReasonCode 헬퍼 분리로 OFF 판정 신규 구현)/IU-0009(evaluatePhase2Candidates를 evaluatePhase3Candidates로 개명·확장, assembleCandidateCommands에 Phase3 3필드 추가+assemblePhase2/3Candidates로 순환복잡도 분리) 갱신. IU-0005(command_arbiter.py)는 설계대로 소스 변경 없음(상수 3개만 constants.py에 추가) 실측 재확인. testsupport/orchestrator_factory.py에 IU-0014~0016 기본값 추가. 기존 tests/test_state_manager.py(전 호출부에 ignitionOnField 인자 추가)/tests_integration/test_it_step2_state_manager.py/test_it_step6_orchestrator_integration.py/test_it_step14_orchestrator_phase2_integration.py(오케스트레이터 생성자 확장에 따른 기계적 동기화만, 신규 IT- 케이스 설계 없음). 단위테스트 137개(Phase2까지 98개+Phase3 신규 39개), 전체 회귀(단위137+통합93+시스템30=260개) 전량 Pass. 품질 게이트 5종(radon cc 최대 복잡도 9[assembleCandidateCommands 분리 전 11 위반을 분리로 해소]; 함수별 순수코드라인 전부 ≤50; pylint duplicate-code 위반 0; pylint invalid-name 위반 0; radon raw 주석비율 29~49%) 신규/변경 파일 전부 실측 통과. Code/SWE.4/Coverage 열 갱신(SWR-003/018/020 대상 3개 행). SWE.5/SWE.6(신규 IT-/ST- 케이스)는 다음 게이트.</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>검토 미실시</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>미승인</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>1.6</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>integration-tester</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Phase 3 SWE.5 — SWR-003/018/020(OEM-FR-002/FR-006/FR-007) 3개 행의 SWE.5(G)/Coverage(I) 열을 갱신(IT-0094~IT-0140 매핑, 함수/Call 커버리지 100% 실측치 반영).</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>초안(검토 미실시)</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>미승인</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>1.7</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>sw-system-tester</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Phase 3 SWE.6(마지막 게이트) - SWR-003/018/020(OEM-FR-002/FR-006/FR-007) 3개 행의 SWE.6(H)/Coverage(I) 열을 갱신(ST-FUNC-0031~0047 매핑, 17/17 Pass, 우선순위 결정표 교차검증 포함). 이 갱신으로 SWR-003/018/020 3개 요구사항의 추적 사슬이 SWE.1부터 SWE.6까지 전부 완성됨. Phase 3 전체 게이트(SWE.1~SWE.6) 완료.</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>초안(검토 미실시)</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
         <is>
           <t>미승인</t>
         </is>
